--- a/SpaceDebris_site_1000/unknown_ULTRASat_attached_to_Centaur-5_SEC_upper.xlsx
+++ b/SpaceDebris_site_1000/unknown_ULTRASat_attached_to_Centaur-5_SEC_upper.xlsx
@@ -452,7002 +452,7002 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.17</v>
+        <v>0.02</v>
       </c>
       <c r="B2" t="n">
-        <v>44674</v>
+        <v>37348</v>
       </c>
       <c r="C2" t="n">
-        <v>100.9</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>12588</v>
+        <v>17698</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105.78</v>
+        <v>0.37</v>
       </c>
       <c r="B3" t="n">
-        <v>42293</v>
+        <v>36575</v>
       </c>
       <c r="C3" t="n">
-        <v>104.3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>13183</v>
+        <v>27813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100.57</v>
+        <v>0.39</v>
       </c>
       <c r="B4" t="n">
-        <v>44682</v>
+        <v>35981</v>
       </c>
       <c r="C4" t="n">
-        <v>98.19</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>27687</v>
+        <v>18186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99.11</v>
+        <v>0.4</v>
       </c>
       <c r="B5" t="n">
-        <v>43289</v>
+        <v>37202</v>
       </c>
       <c r="C5" t="n">
-        <v>98.43000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="D5" t="n">
-        <v>26734</v>
+        <v>19433</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101.57</v>
+        <v>0.62</v>
       </c>
       <c r="B6" t="n">
-        <v>46147</v>
+        <v>35867</v>
       </c>
       <c r="C6" t="n">
-        <v>103.43</v>
+        <v>0.29</v>
       </c>
       <c r="D6" t="n">
-        <v>15295</v>
+        <v>17557</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>93.20999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="B7" t="n">
-        <v>29040</v>
+        <v>36073</v>
       </c>
       <c r="C7" t="n">
-        <v>91.68000000000001</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>28571</v>
+        <v>27907</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99.8</v>
+        <v>2.46</v>
       </c>
       <c r="B8" t="n">
-        <v>44086</v>
+        <v>38025</v>
       </c>
       <c r="C8" t="n">
-        <v>100.38</v>
+        <v>6.92</v>
       </c>
       <c r="D8" t="n">
-        <v>13086</v>
+        <v>21592</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107.94</v>
+        <v>2.64</v>
       </c>
       <c r="B9" t="n">
-        <v>41477</v>
+        <v>36581</v>
       </c>
       <c r="C9" t="n">
-        <v>110.32</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>22146</v>
+        <v>16827</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95.78</v>
+        <v>3.26</v>
       </c>
       <c r="B10" t="n">
-        <v>34635</v>
+        <v>33970</v>
       </c>
       <c r="C10" t="n">
-        <v>92.56</v>
+        <v>1.6</v>
       </c>
       <c r="D10" t="n">
-        <v>14563</v>
+        <v>17316</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109.93</v>
+        <v>3.37</v>
       </c>
       <c r="B11" t="n">
-        <v>29770</v>
+        <v>36555</v>
       </c>
       <c r="C11" t="n">
-        <v>111.88</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>23047</v>
+        <v>19037</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>91.36</v>
+        <v>3.53</v>
       </c>
       <c r="B12" t="n">
-        <v>25057</v>
+        <v>36547</v>
       </c>
       <c r="C12" t="n">
-        <v>92.09</v>
+        <v>9.65</v>
       </c>
       <c r="D12" t="n">
-        <v>20283</v>
+        <v>13495</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106.74</v>
+        <v>4.01</v>
       </c>
       <c r="B13" t="n">
-        <v>43714</v>
+        <v>34467</v>
       </c>
       <c r="C13" t="n">
-        <v>103.69</v>
+        <v>11.52</v>
       </c>
       <c r="D13" t="n">
-        <v>17245</v>
+        <v>11510</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108.15</v>
+        <v>4.23</v>
       </c>
       <c r="B14" t="n">
-        <v>36225</v>
+        <v>37151</v>
       </c>
       <c r="C14" t="n">
-        <v>108.19</v>
+        <v>16.66</v>
       </c>
       <c r="D14" t="n">
-        <v>28147</v>
+        <v>11177</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>90.31</v>
+        <v>4.68</v>
       </c>
       <c r="B15" t="n">
-        <v>24207</v>
+        <v>34298</v>
       </c>
       <c r="C15" t="n">
-        <v>87.43000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="D15" t="n">
-        <v>16743</v>
+        <v>28051</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>92.59</v>
+        <v>4.94</v>
       </c>
       <c r="B16" t="n">
-        <v>25122</v>
+        <v>33571</v>
       </c>
       <c r="C16" t="n">
-        <v>94.13</v>
+        <v>6.08</v>
       </c>
       <c r="D16" t="n">
-        <v>11669</v>
+        <v>11216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102.45</v>
+        <v>5.51</v>
       </c>
       <c r="B17" t="n">
-        <v>46454</v>
+        <v>33746</v>
       </c>
       <c r="C17" t="n">
-        <v>103.23</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>15131</v>
+        <v>24161</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95.75</v>
+        <v>5.58</v>
       </c>
       <c r="B18" t="n">
-        <v>36473</v>
+        <v>34087</v>
       </c>
       <c r="C18" t="n">
-        <v>94.92</v>
+        <v>18.14</v>
       </c>
       <c r="D18" t="n">
-        <v>25857</v>
+        <v>13468</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>14.29</v>
+        <v>5.82</v>
       </c>
       <c r="B19" t="n">
-        <v>23033</v>
+        <v>34523</v>
       </c>
       <c r="C19" t="n">
-        <v>15.32</v>
+        <v>5.02</v>
       </c>
       <c r="D19" t="n">
-        <v>13607</v>
+        <v>13458</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>99.16</v>
+        <v>6.23</v>
       </c>
       <c r="B20" t="n">
-        <v>43539</v>
+        <v>34691</v>
       </c>
       <c r="C20" t="n">
-        <v>98.75</v>
+        <v>10.57</v>
       </c>
       <c r="D20" t="n">
-        <v>21449</v>
+        <v>23596</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>106.9</v>
+        <v>6.74</v>
       </c>
       <c r="B21" t="n">
-        <v>44255</v>
+        <v>33186</v>
       </c>
       <c r="C21" t="n">
-        <v>103.32</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>19731</v>
+        <v>25217</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97.33</v>
+        <v>7.53</v>
       </c>
       <c r="B22" t="n">
-        <v>38931</v>
+        <v>35088</v>
       </c>
       <c r="C22" t="n">
-        <v>102.14</v>
+        <v>13.16</v>
       </c>
       <c r="D22" t="n">
-        <v>27567</v>
+        <v>19543</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110.21</v>
+        <v>7.56</v>
       </c>
       <c r="B23" t="n">
-        <v>31355</v>
+        <v>34377</v>
       </c>
       <c r="C23" t="n">
-        <v>109.64</v>
+        <v>0.76</v>
       </c>
       <c r="D23" t="n">
-        <v>25114</v>
+        <v>25261</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111.9</v>
+        <v>7.64</v>
       </c>
       <c r="B24" t="n">
-        <v>27115</v>
+        <v>33269</v>
       </c>
       <c r="C24" t="n">
-        <v>110</v>
+        <v>6.24</v>
       </c>
       <c r="D24" t="n">
-        <v>10715</v>
+        <v>21339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>150.97</v>
+        <v>7.79</v>
       </c>
       <c r="B25" t="n">
-        <v>25762</v>
+        <v>32454</v>
       </c>
       <c r="C25" t="n">
-        <v>157.76</v>
+        <v>7.55</v>
       </c>
       <c r="D25" t="n">
-        <v>11087</v>
+        <v>14684</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>99.54000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="B26" t="n">
-        <v>42941</v>
+        <v>32614</v>
       </c>
       <c r="C26" t="n">
-        <v>99.34999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="D26" t="n">
-        <v>26321</v>
+        <v>16218</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>174.51</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="B27" t="n">
-        <v>25414</v>
+        <v>32362</v>
       </c>
       <c r="C27" t="n">
-        <v>180</v>
+        <v>20.33</v>
       </c>
       <c r="D27" t="n">
-        <v>14461</v>
+        <v>19890</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111.61</v>
+        <v>10.53</v>
       </c>
       <c r="B28" t="n">
-        <v>26580</v>
+        <v>31251</v>
       </c>
       <c r="C28" t="n">
-        <v>108.32</v>
+        <v>15.51</v>
       </c>
       <c r="D28" t="n">
-        <v>15120</v>
+        <v>22408</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113.67</v>
+        <v>11.15</v>
       </c>
       <c r="B29" t="n">
-        <v>25952</v>
+        <v>30775</v>
       </c>
       <c r="C29" t="n">
-        <v>109.96</v>
+        <v>19.74</v>
       </c>
       <c r="D29" t="n">
-        <v>16369</v>
+        <v>15957</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109.76</v>
+        <v>11.83</v>
       </c>
       <c r="B30" t="n">
-        <v>33428</v>
+        <v>28077</v>
       </c>
       <c r="C30" t="n">
-        <v>110.18</v>
+        <v>9.24</v>
       </c>
       <c r="D30" t="n">
-        <v>19403</v>
+        <v>10488</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>99.25</v>
+        <v>12.13</v>
       </c>
       <c r="B31" t="n">
-        <v>41578</v>
+        <v>30430</v>
       </c>
       <c r="C31" t="n">
-        <v>97.3</v>
+        <v>10.11</v>
       </c>
       <c r="D31" t="n">
-        <v>26432</v>
+        <v>27588</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>94.06</v>
+        <v>12.29</v>
       </c>
       <c r="B32" t="n">
-        <v>30402</v>
+        <v>31356</v>
       </c>
       <c r="C32" t="n">
-        <v>94.67</v>
+        <v>7.75</v>
       </c>
       <c r="D32" t="n">
-        <v>27619</v>
+        <v>16169</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>63.05</v>
+        <v>12.33</v>
       </c>
       <c r="B33" t="n">
-        <v>24687</v>
+        <v>29947</v>
       </c>
       <c r="C33" t="n">
-        <v>61.28</v>
+        <v>4.03</v>
       </c>
       <c r="D33" t="n">
-        <v>22078</v>
+        <v>17485</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104.39</v>
+        <v>12.79</v>
       </c>
       <c r="B34" t="n">
-        <v>45530</v>
+        <v>29150</v>
       </c>
       <c r="C34" t="n">
-        <v>106.78</v>
+        <v>8.42</v>
       </c>
       <c r="D34" t="n">
-        <v>25940</v>
+        <v>28169</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>90.26000000000001</v>
+        <v>13.01</v>
       </c>
       <c r="B35" t="n">
-        <v>23957</v>
+        <v>29657</v>
       </c>
       <c r="C35" t="n">
-        <v>87.59</v>
+        <v>7.24</v>
       </c>
       <c r="D35" t="n">
-        <v>17336</v>
+        <v>17374</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111.01</v>
+        <v>14.55</v>
       </c>
       <c r="B36" t="n">
-        <v>29168</v>
+        <v>26370</v>
       </c>
       <c r="C36" t="n">
-        <v>114.76</v>
+        <v>15.09</v>
       </c>
       <c r="D36" t="n">
-        <v>26602</v>
+        <v>19788</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>90.42</v>
+        <v>14.59</v>
       </c>
       <c r="B37" t="n">
-        <v>24521</v>
+        <v>24882</v>
       </c>
       <c r="C37" t="n">
-        <v>88.06</v>
+        <v>2.6</v>
       </c>
       <c r="D37" t="n">
-        <v>23000</v>
+        <v>12798</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>99.17</v>
+        <v>15.38</v>
       </c>
       <c r="B38" t="n">
-        <v>44459</v>
+        <v>25726</v>
       </c>
       <c r="C38" t="n">
-        <v>96.48</v>
+        <v>19.12</v>
       </c>
       <c r="D38" t="n">
-        <v>15788</v>
+        <v>11076</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>101.38</v>
+        <v>15.45</v>
       </c>
       <c r="B39" t="n">
-        <v>45699</v>
+        <v>28386</v>
       </c>
       <c r="C39" t="n">
-        <v>102.76</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>19322</v>
+        <v>29579</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111.16</v>
+        <v>15.51</v>
       </c>
       <c r="B40" t="n">
-        <v>28324</v>
+        <v>27743</v>
       </c>
       <c r="C40" t="n">
-        <v>111.5</v>
+        <v>16.79</v>
       </c>
       <c r="D40" t="n">
-        <v>25587</v>
+        <v>15999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>55.67</v>
+        <v>16.14</v>
       </c>
       <c r="B41" t="n">
-        <v>25330</v>
+        <v>27065</v>
       </c>
       <c r="C41" t="n">
-        <v>57.61</v>
+        <v>14.5</v>
       </c>
       <c r="D41" t="n">
-        <v>25352</v>
+        <v>29355</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>108.71</v>
+        <v>16.17</v>
       </c>
       <c r="B42" t="n">
-        <v>37429</v>
+        <v>24037</v>
       </c>
       <c r="C42" t="n">
-        <v>110.55</v>
+        <v>21.54</v>
       </c>
       <c r="D42" t="n">
-        <v>15114</v>
+        <v>12556</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>108.24</v>
+        <v>17</v>
       </c>
       <c r="B43" t="n">
-        <v>36855</v>
+        <v>25430</v>
       </c>
       <c r="C43" t="n">
-        <v>103.9</v>
+        <v>11.46</v>
       </c>
       <c r="D43" t="n">
-        <v>18099</v>
+        <v>27733</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>105.95</v>
+        <v>17.03</v>
       </c>
       <c r="B44" t="n">
-        <v>43902</v>
+        <v>25397</v>
       </c>
       <c r="C44" t="n">
-        <v>107.35</v>
+        <v>13.79</v>
       </c>
       <c r="D44" t="n">
-        <v>21913</v>
+        <v>24397</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>94.12</v>
+        <v>17.71</v>
       </c>
       <c r="B45" t="n">
-        <v>32195</v>
+        <v>24946</v>
       </c>
       <c r="C45" t="n">
-        <v>95.98</v>
+        <v>23.68</v>
       </c>
       <c r="D45" t="n">
-        <v>22206</v>
+        <v>12842</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>37.87</v>
+        <v>17.84</v>
       </c>
       <c r="B46" t="n">
-        <v>21792</v>
+        <v>24867</v>
       </c>
       <c r="C46" t="n">
-        <v>38.78</v>
+        <v>20.73</v>
       </c>
       <c r="D46" t="n">
-        <v>10919</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>176.04</v>
+        <v>18</v>
       </c>
       <c r="B47" t="n">
-        <v>22737</v>
+        <v>25175</v>
       </c>
       <c r="C47" t="n">
-        <v>180</v>
+        <v>20.77</v>
       </c>
       <c r="D47" t="n">
-        <v>17729</v>
+        <v>10502</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>107.29</v>
+        <v>18.2</v>
       </c>
       <c r="B48" t="n">
-        <v>39609</v>
+        <v>22484</v>
       </c>
       <c r="C48" t="n">
-        <v>103.82</v>
+        <v>16.78</v>
       </c>
       <c r="D48" t="n">
-        <v>15087</v>
+        <v>27612</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>103.95</v>
+        <v>18.29</v>
       </c>
       <c r="B49" t="n">
-        <v>44912</v>
+        <v>24757</v>
       </c>
       <c r="C49" t="n">
-        <v>104.61</v>
+        <v>18.03</v>
       </c>
       <c r="D49" t="n">
-        <v>10707</v>
+        <v>14008</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>97.41</v>
+        <v>18.58</v>
       </c>
       <c r="B50" t="n">
-        <v>38307</v>
+        <v>21016</v>
       </c>
       <c r="C50" t="n">
-        <v>95.19</v>
+        <v>15.01</v>
       </c>
       <c r="D50" t="n">
-        <v>21962</v>
+        <v>21502</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>15.53</v>
+        <v>18.61</v>
       </c>
       <c r="B51" t="n">
-        <v>23085</v>
+        <v>23803</v>
       </c>
       <c r="C51" t="n">
-        <v>15.64</v>
+        <v>13.68</v>
       </c>
       <c r="D51" t="n">
-        <v>24044</v>
+        <v>25855</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>149.57</v>
+        <v>18.75</v>
       </c>
       <c r="B52" t="n">
-        <v>22038</v>
+        <v>25281</v>
       </c>
       <c r="C52" t="n">
-        <v>150.73</v>
+        <v>18.65</v>
       </c>
       <c r="D52" t="n">
-        <v>15969</v>
+        <v>12257</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>98.42</v>
+        <v>20.32</v>
       </c>
       <c r="B53" t="n">
-        <v>41735</v>
+        <v>25392</v>
       </c>
       <c r="C53" t="n">
-        <v>98.87</v>
+        <v>27.07</v>
       </c>
       <c r="D53" t="n">
-        <v>28061</v>
+        <v>11664</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>102.62</v>
+        <v>20.54</v>
       </c>
       <c r="B54" t="n">
-        <v>48806</v>
+        <v>23297</v>
       </c>
       <c r="C54" t="n">
-        <v>101.63</v>
+        <v>15.42</v>
       </c>
       <c r="D54" t="n">
-        <v>28961</v>
+        <v>27375</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>155.74</v>
+        <v>21.09</v>
       </c>
       <c r="B55" t="n">
-        <v>25181</v>
+        <v>23686</v>
       </c>
       <c r="C55" t="n">
-        <v>158.22</v>
+        <v>11.56</v>
       </c>
       <c r="D55" t="n">
-        <v>15845</v>
+        <v>15076</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>105.11</v>
+        <v>21.5</v>
       </c>
       <c r="B56" t="n">
-        <v>42829</v>
+        <v>22116</v>
       </c>
       <c r="C56" t="n">
-        <v>108.77</v>
+        <v>15.05</v>
       </c>
       <c r="D56" t="n">
-        <v>15698</v>
+        <v>11974</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>104.53</v>
+        <v>21.58</v>
       </c>
       <c r="B57" t="n">
-        <v>47040</v>
+        <v>22746</v>
       </c>
       <c r="C57" t="n">
-        <v>103.41</v>
+        <v>27.73</v>
       </c>
       <c r="D57" t="n">
-        <v>24334</v>
+        <v>13804</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>104.07</v>
+        <v>21.6</v>
       </c>
       <c r="B58" t="n">
-        <v>47239</v>
+        <v>22758</v>
       </c>
       <c r="C58" t="n">
-        <v>103.95</v>
+        <v>23.03</v>
       </c>
       <c r="D58" t="n">
-        <v>13914</v>
+        <v>15195</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111.89</v>
+        <v>21.81</v>
       </c>
       <c r="B59" t="n">
-        <v>24273</v>
+        <v>24955</v>
       </c>
       <c r="C59" t="n">
-        <v>112.08</v>
+        <v>22.71</v>
       </c>
       <c r="D59" t="n">
-        <v>28360</v>
+        <v>11646</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>104.07</v>
+        <v>22.19</v>
       </c>
       <c r="B60" t="n">
-        <v>45839</v>
+        <v>23090</v>
       </c>
       <c r="C60" t="n">
-        <v>101.25</v>
+        <v>28.36</v>
       </c>
       <c r="D60" t="n">
-        <v>29485</v>
+        <v>28962</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119.65</v>
+        <v>23.77</v>
       </c>
       <c r="B61" t="n">
-        <v>23561</v>
+        <v>23524</v>
       </c>
       <c r="C61" t="n">
-        <v>120.29</v>
+        <v>30.14</v>
       </c>
       <c r="D61" t="n">
-        <v>20974</v>
+        <v>22043</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>45.87</v>
+        <v>23.81</v>
       </c>
       <c r="B62" t="n">
-        <v>23283</v>
+        <v>21413</v>
       </c>
       <c r="C62" t="n">
-        <v>46.13</v>
+        <v>32.04</v>
       </c>
       <c r="D62" t="n">
-        <v>19410</v>
+        <v>13619</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>98.47</v>
+        <v>23.83</v>
       </c>
       <c r="B63" t="n">
-        <v>42735</v>
+        <v>23434</v>
       </c>
       <c r="C63" t="n">
-        <v>98.12</v>
+        <v>27.23</v>
       </c>
       <c r="D63" t="n">
-        <v>14369</v>
+        <v>13007</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>110.09</v>
+        <v>24.47</v>
       </c>
       <c r="B64" t="n">
-        <v>32498</v>
+        <v>21994</v>
       </c>
       <c r="C64" t="n">
-        <v>113.77</v>
+        <v>29.52</v>
       </c>
       <c r="D64" t="n">
-        <v>24008</v>
+        <v>29901</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>108.49</v>
+        <v>25.55</v>
       </c>
       <c r="B65" t="n">
-        <v>36404</v>
+        <v>22466</v>
       </c>
       <c r="C65" t="n">
-        <v>107.22</v>
+        <v>14.42</v>
       </c>
       <c r="D65" t="n">
-        <v>16179</v>
+        <v>21554</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>176.37</v>
+        <v>25.96</v>
       </c>
       <c r="B66" t="n">
-        <v>24306</v>
+        <v>25266</v>
       </c>
       <c r="C66" t="n">
-        <v>170.92</v>
+        <v>25.65</v>
       </c>
       <c r="D66" t="n">
-        <v>29258</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112.05</v>
+        <v>26.08</v>
       </c>
       <c r="B67" t="n">
-        <v>27689</v>
+        <v>21061</v>
       </c>
       <c r="C67" t="n">
-        <v>113.84</v>
+        <v>25.32</v>
       </c>
       <c r="D67" t="n">
-        <v>17970</v>
+        <v>28542</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>94.14</v>
+        <v>26.15</v>
       </c>
       <c r="B68" t="n">
-        <v>33835</v>
+        <v>21337</v>
       </c>
       <c r="C68" t="n">
-        <v>94.15000000000001</v>
+        <v>23.56</v>
       </c>
       <c r="D68" t="n">
-        <v>25702</v>
+        <v>18339</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>111.15</v>
+        <v>26.22</v>
       </c>
       <c r="B69" t="n">
-        <v>29267</v>
+        <v>21499</v>
       </c>
       <c r="C69" t="n">
-        <v>114.53</v>
+        <v>21.63</v>
       </c>
       <c r="D69" t="n">
-        <v>14234</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>108.09</v>
+        <v>26.41</v>
       </c>
       <c r="B70" t="n">
-        <v>37771</v>
+        <v>23420</v>
       </c>
       <c r="C70" t="n">
-        <v>110.11</v>
+        <v>24.01</v>
       </c>
       <c r="D70" t="n">
-        <v>25522</v>
+        <v>18053</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>116.91</v>
+        <v>26.43</v>
       </c>
       <c r="B71" t="n">
-        <v>21978</v>
+        <v>22706</v>
       </c>
       <c r="C71" t="n">
-        <v>113.67</v>
+        <v>25.98</v>
       </c>
       <c r="D71" t="n">
-        <v>22679</v>
+        <v>26872</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>78.17</v>
+        <v>26.59</v>
       </c>
       <c r="B72" t="n">
-        <v>23056</v>
+        <v>20661</v>
       </c>
       <c r="C72" t="n">
-        <v>78.56</v>
+        <v>30.15</v>
       </c>
       <c r="D72" t="n">
-        <v>27132</v>
+        <v>26338</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>112.81</v>
+        <v>27.14</v>
       </c>
       <c r="B73" t="n">
-        <v>23864</v>
+        <v>20234</v>
       </c>
       <c r="C73" t="n">
-        <v>114.25</v>
+        <v>26.38</v>
       </c>
       <c r="D73" t="n">
-        <v>15859</v>
+        <v>26809</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113.78</v>
+        <v>27.25</v>
       </c>
       <c r="B74" t="n">
-        <v>23120</v>
+        <v>21263</v>
       </c>
       <c r="C74" t="n">
-        <v>110.83</v>
+        <v>35.05</v>
       </c>
       <c r="D74" t="n">
-        <v>17651</v>
+        <v>19988</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113.03</v>
+        <v>27.94</v>
       </c>
       <c r="B75" t="n">
-        <v>23039</v>
+        <v>21310</v>
       </c>
       <c r="C75" t="n">
-        <v>112.14</v>
+        <v>38.19</v>
       </c>
       <c r="D75" t="n">
-        <v>17969</v>
+        <v>22296</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>105.79</v>
+        <v>28.06</v>
       </c>
       <c r="B76" t="n">
-        <v>45012</v>
+        <v>23712</v>
       </c>
       <c r="C76" t="n">
-        <v>108.41</v>
+        <v>31.89</v>
       </c>
       <c r="D76" t="n">
-        <v>28593</v>
+        <v>28458</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>109.63</v>
+        <v>28.79</v>
       </c>
       <c r="B77" t="n">
-        <v>30282</v>
+        <v>22198</v>
       </c>
       <c r="C77" t="n">
-        <v>114.69</v>
+        <v>18.55</v>
       </c>
       <c r="D77" t="n">
-        <v>13329</v>
+        <v>15308</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>112.86</v>
+        <v>30.03</v>
       </c>
       <c r="B78" t="n">
-        <v>25223</v>
+        <v>21671</v>
       </c>
       <c r="C78" t="n">
-        <v>109.83</v>
+        <v>38.52</v>
       </c>
       <c r="D78" t="n">
-        <v>24670</v>
+        <v>24267</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>73.5</v>
+        <v>30.4</v>
       </c>
       <c r="B79" t="n">
-        <v>22720</v>
+        <v>17696</v>
       </c>
       <c r="C79" t="n">
-        <v>70.63</v>
+        <v>18.79</v>
       </c>
       <c r="D79" t="n">
-        <v>16369</v>
+        <v>11258</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>91.33</v>
+        <v>30.57</v>
       </c>
       <c r="B80" t="n">
-        <v>23444</v>
+        <v>20999</v>
       </c>
       <c r="C80" t="n">
-        <v>92.34</v>
+        <v>35.48</v>
       </c>
       <c r="D80" t="n">
-        <v>29184</v>
+        <v>18795</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>105.44</v>
+        <v>30.76</v>
       </c>
       <c r="B81" t="n">
-        <v>45311</v>
+        <v>22653</v>
       </c>
       <c r="C81" t="n">
-        <v>105.45</v>
+        <v>27.6</v>
       </c>
       <c r="D81" t="n">
-        <v>25766</v>
+        <v>12832</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>92.59999999999999</v>
+        <v>31.21</v>
       </c>
       <c r="B82" t="n">
-        <v>28381</v>
+        <v>18654</v>
       </c>
       <c r="C82" t="n">
-        <v>96.03</v>
+        <v>26.54</v>
       </c>
       <c r="D82" t="n">
-        <v>25844</v>
+        <v>17493</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>102.3</v>
+        <v>31.46</v>
       </c>
       <c r="B83" t="n">
-        <v>46692</v>
+        <v>20529</v>
       </c>
       <c r="C83" t="n">
-        <v>104.37</v>
+        <v>26.1</v>
       </c>
       <c r="D83" t="n">
-        <v>23885</v>
+        <v>23187</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>8.18</v>
+        <v>32.1</v>
       </c>
       <c r="B84" t="n">
-        <v>23496</v>
+        <v>20129</v>
       </c>
       <c r="C84" t="n">
-        <v>9.300000000000001</v>
+        <v>24.49</v>
       </c>
       <c r="D84" t="n">
-        <v>12952</v>
+        <v>29388</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>94.52</v>
+        <v>32.25</v>
       </c>
       <c r="B85" t="n">
-        <v>32611</v>
+        <v>20940</v>
       </c>
       <c r="C85" t="n">
-        <v>96.22</v>
+        <v>28.72</v>
       </c>
       <c r="D85" t="n">
-        <v>23216</v>
+        <v>26664</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112.35</v>
+        <v>32.53</v>
       </c>
       <c r="B86" t="n">
-        <v>27274</v>
+        <v>18835</v>
       </c>
       <c r="C86" t="n">
-        <v>111.33</v>
+        <v>37.06</v>
       </c>
       <c r="D86" t="n">
-        <v>29466</v>
+        <v>10201</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112.52</v>
+        <v>32.68</v>
       </c>
       <c r="B87" t="n">
-        <v>25938</v>
+        <v>21888</v>
       </c>
       <c r="C87" t="n">
-        <v>108.52</v>
+        <v>45.77</v>
       </c>
       <c r="D87" t="n">
-        <v>26229</v>
+        <v>11417</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>93.09</v>
+        <v>32.8</v>
       </c>
       <c r="B88" t="n">
-        <v>30233</v>
+        <v>21836</v>
       </c>
       <c r="C88" t="n">
-        <v>93.59</v>
+        <v>33.69</v>
       </c>
       <c r="D88" t="n">
-        <v>13294</v>
+        <v>27318</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>96.91</v>
+        <v>32.81</v>
       </c>
       <c r="B89" t="n">
-        <v>41721</v>
+        <v>19760</v>
       </c>
       <c r="C89" t="n">
-        <v>97.83</v>
+        <v>45.04</v>
       </c>
       <c r="D89" t="n">
-        <v>23521</v>
+        <v>24695</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>105.19</v>
+        <v>32.91</v>
       </c>
       <c r="B90" t="n">
-        <v>43347</v>
+        <v>20608</v>
       </c>
       <c r="C90" t="n">
-        <v>104.63</v>
+        <v>37.09</v>
       </c>
       <c r="D90" t="n">
-        <v>24145</v>
+        <v>10056</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>94.59</v>
+        <v>32.97</v>
       </c>
       <c r="B91" t="n">
-        <v>34049</v>
+        <v>20194</v>
       </c>
       <c r="C91" t="n">
-        <v>90.73</v>
+        <v>32.04</v>
       </c>
       <c r="D91" t="n">
-        <v>13245</v>
+        <v>16361</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>109.16</v>
+        <v>33.05</v>
       </c>
       <c r="B92" t="n">
-        <v>34305</v>
+        <v>19530</v>
       </c>
       <c r="C92" t="n">
-        <v>111.34</v>
+        <v>31.01</v>
       </c>
       <c r="D92" t="n">
-        <v>14796</v>
+        <v>24869</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>108.41</v>
+        <v>33.09</v>
       </c>
       <c r="B93" t="n">
-        <v>37983</v>
+        <v>19533</v>
       </c>
       <c r="C93" t="n">
-        <v>108.46</v>
+        <v>36.14</v>
       </c>
       <c r="D93" t="n">
-        <v>12754</v>
+        <v>20617</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>103.45</v>
+        <v>33.18</v>
       </c>
       <c r="B94" t="n">
-        <v>47592</v>
+        <v>21047</v>
       </c>
       <c r="C94" t="n">
-        <v>100.04</v>
+        <v>42.01</v>
       </c>
       <c r="D94" t="n">
-        <v>15746</v>
+        <v>24829</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>102.2</v>
+        <v>34.58</v>
       </c>
       <c r="B95" t="n">
-        <v>45378</v>
+        <v>20218</v>
       </c>
       <c r="C95" t="n">
-        <v>105.35</v>
+        <v>52.16</v>
       </c>
       <c r="D95" t="n">
-        <v>24030</v>
+        <v>15040</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>112.49</v>
+        <v>34.88</v>
       </c>
       <c r="B96" t="n">
-        <v>28225</v>
+        <v>24082</v>
       </c>
       <c r="C96" t="n">
-        <v>115.29</v>
+        <v>43.94</v>
       </c>
       <c r="D96" t="n">
-        <v>23548</v>
+        <v>17058</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>100.94</v>
+        <v>34.88</v>
       </c>
       <c r="B97" t="n">
-        <v>43886</v>
+        <v>22924</v>
       </c>
       <c r="C97" t="n">
-        <v>100.58</v>
+        <v>35.53</v>
       </c>
       <c r="D97" t="n">
-        <v>24983</v>
+        <v>18658</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>112.68</v>
+        <v>35.15</v>
       </c>
       <c r="B98" t="n">
-        <v>27037</v>
+        <v>20660</v>
       </c>
       <c r="C98" t="n">
-        <v>114.07</v>
+        <v>39.99</v>
       </c>
       <c r="D98" t="n">
-        <v>23805</v>
+        <v>15186</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>94.65000000000001</v>
+        <v>35.27</v>
       </c>
       <c r="B99" t="n">
-        <v>32582</v>
+        <v>23257</v>
       </c>
       <c r="C99" t="n">
-        <v>90.84</v>
+        <v>35.16</v>
       </c>
       <c r="D99" t="n">
-        <v>28704</v>
+        <v>19711</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>103.09</v>
+        <v>35.34</v>
       </c>
       <c r="B100" t="n">
-        <v>47819</v>
+        <v>21231</v>
       </c>
       <c r="C100" t="n">
-        <v>99.59</v>
+        <v>28.63</v>
       </c>
       <c r="D100" t="n">
-        <v>15899</v>
+        <v>23361</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>93.41</v>
+        <v>35.39</v>
       </c>
       <c r="B101" t="n">
-        <v>30948</v>
+        <v>21469</v>
       </c>
       <c r="C101" t="n">
-        <v>92.94</v>
+        <v>43.52</v>
       </c>
       <c r="D101" t="n">
-        <v>12181</v>
+        <v>17758</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>110.2</v>
+        <v>35.57</v>
       </c>
       <c r="B102" t="n">
-        <v>27911</v>
+        <v>21471</v>
       </c>
       <c r="C102" t="n">
-        <v>112.01</v>
+        <v>35.67</v>
       </c>
       <c r="D102" t="n">
-        <v>12199</v>
+        <v>19122</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>102.85</v>
+        <v>35.71</v>
       </c>
       <c r="B103" t="n">
-        <v>46348</v>
+        <v>22451</v>
       </c>
       <c r="C103" t="n">
-        <v>106.64</v>
+        <v>26.46</v>
       </c>
       <c r="D103" t="n">
-        <v>21119</v>
+        <v>22833</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>113.96</v>
+        <v>35.82</v>
       </c>
       <c r="B104" t="n">
-        <v>22759</v>
+        <v>19750</v>
       </c>
       <c r="C104" t="n">
-        <v>112.6</v>
+        <v>44.81</v>
       </c>
       <c r="D104" t="n">
-        <v>21581</v>
+        <v>14505</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>104.25</v>
+        <v>36.39</v>
       </c>
       <c r="B105" t="n">
-        <v>47729</v>
+        <v>21366</v>
       </c>
       <c r="C105" t="n">
-        <v>102.17</v>
+        <v>44.02</v>
       </c>
       <c r="D105" t="n">
-        <v>24126</v>
+        <v>16177</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>108.49</v>
+        <v>36.92</v>
       </c>
       <c r="B106" t="n">
-        <v>37082</v>
+        <v>22957</v>
       </c>
       <c r="C106" t="n">
-        <v>107.28</v>
+        <v>48.28</v>
       </c>
       <c r="D106" t="n">
-        <v>29876</v>
+        <v>19920</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>41.48</v>
+        <v>37.56</v>
       </c>
       <c r="B107" t="n">
-        <v>22367</v>
+        <v>21791</v>
       </c>
       <c r="C107" t="n">
-        <v>43.62</v>
+        <v>36.03</v>
       </c>
       <c r="D107" t="n">
-        <v>24160</v>
+        <v>21148</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>102.3</v>
+        <v>37.58</v>
       </c>
       <c r="B108" t="n">
-        <v>47910</v>
+        <v>22266</v>
       </c>
       <c r="C108" t="n">
-        <v>99.87</v>
+        <v>35.03</v>
       </c>
       <c r="D108" t="n">
-        <v>14042</v>
+        <v>24327</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>113</v>
+        <v>38.71</v>
       </c>
       <c r="B109" t="n">
-        <v>29092</v>
+        <v>23454</v>
       </c>
       <c r="C109" t="n">
-        <v>111.8</v>
+        <v>36.53</v>
       </c>
       <c r="D109" t="n">
-        <v>22225</v>
+        <v>15680</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>99.25</v>
+        <v>38.81</v>
       </c>
       <c r="B110" t="n">
-        <v>43037</v>
+        <v>19243</v>
       </c>
       <c r="C110" t="n">
-        <v>100.63</v>
+        <v>35.41</v>
       </c>
       <c r="D110" t="n">
-        <v>28893</v>
+        <v>12890</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>96.70999999999999</v>
+        <v>38.82</v>
       </c>
       <c r="B111" t="n">
-        <v>36800</v>
+        <v>21799</v>
       </c>
       <c r="C111" t="n">
-        <v>94.77</v>
+        <v>43.83</v>
       </c>
       <c r="D111" t="n">
-        <v>15066</v>
+        <v>16944</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130.02</v>
+        <v>39</v>
       </c>
       <c r="B112" t="n">
-        <v>24071</v>
+        <v>22390</v>
       </c>
       <c r="C112" t="n">
-        <v>128.58</v>
+        <v>45.86</v>
       </c>
       <c r="D112" t="n">
-        <v>16454</v>
+        <v>26564</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>107.19</v>
+        <v>39.79</v>
       </c>
       <c r="B113" t="n">
-        <v>42336</v>
+        <v>21921</v>
       </c>
       <c r="C113" t="n">
-        <v>105.38</v>
+        <v>43.05</v>
       </c>
       <c r="D113" t="n">
-        <v>12791</v>
+        <v>24581</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129.04</v>
+        <v>39.85</v>
       </c>
       <c r="B114" t="n">
-        <v>22049</v>
+        <v>20534</v>
       </c>
       <c r="C114" t="n">
-        <v>130.88</v>
+        <v>42.43</v>
       </c>
       <c r="D114" t="n">
-        <v>11782</v>
+        <v>20314</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>103.52</v>
+        <v>39.99</v>
       </c>
       <c r="B115" t="n">
-        <v>46718</v>
+        <v>20437</v>
       </c>
       <c r="C115" t="n">
-        <v>104.24</v>
+        <v>44.58</v>
       </c>
       <c r="D115" t="n">
-        <v>12663</v>
+        <v>26252</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>101.67</v>
+        <v>40.65</v>
       </c>
       <c r="B116" t="n">
-        <v>45613</v>
+        <v>21767</v>
       </c>
       <c r="C116" t="n">
-        <v>106.39</v>
+        <v>40.46</v>
       </c>
       <c r="D116" t="n">
-        <v>13267</v>
+        <v>16653</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>37.88</v>
+        <v>40.89</v>
       </c>
       <c r="B117" t="n">
-        <v>23780</v>
+        <v>20711</v>
       </c>
       <c r="C117" t="n">
-        <v>39.6</v>
+        <v>42.07</v>
       </c>
       <c r="D117" t="n">
-        <v>19506</v>
+        <v>23746</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>114</v>
+        <v>41.14</v>
       </c>
       <c r="B118" t="n">
-        <v>25587</v>
+        <v>20448</v>
       </c>
       <c r="C118" t="n">
-        <v>117.08</v>
+        <v>38.81</v>
       </c>
       <c r="D118" t="n">
-        <v>24645</v>
+        <v>27786</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>114.95</v>
+        <v>41.75</v>
       </c>
       <c r="B119" t="n">
-        <v>20234</v>
+        <v>20017</v>
       </c>
       <c r="C119" t="n">
-        <v>117.98</v>
+        <v>40.8</v>
       </c>
       <c r="D119" t="n">
-        <v>22149</v>
+        <v>16444</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>91.84999999999999</v>
+        <v>42.37</v>
       </c>
       <c r="B120" t="n">
-        <v>24365</v>
+        <v>21739</v>
       </c>
       <c r="C120" t="n">
-        <v>94.03</v>
+        <v>34.15</v>
       </c>
       <c r="D120" t="n">
-        <v>19801</v>
+        <v>25895</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>77.38</v>
+        <v>42.63</v>
       </c>
       <c r="B121" t="n">
-        <v>23467</v>
+        <v>22492</v>
       </c>
       <c r="C121" t="n">
-        <v>75.01000000000001</v>
+        <v>37.54</v>
       </c>
       <c r="D121" t="n">
-        <v>26084</v>
+        <v>28597</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>114.7</v>
+        <v>43.55</v>
       </c>
       <c r="B122" t="n">
-        <v>21109</v>
+        <v>21159</v>
       </c>
       <c r="C122" t="n">
-        <v>118.63</v>
+        <v>43.89</v>
       </c>
       <c r="D122" t="n">
-        <v>19277</v>
+        <v>25292</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>114.54</v>
+        <v>43.62</v>
       </c>
       <c r="B123" t="n">
-        <v>22243</v>
+        <v>20748</v>
       </c>
       <c r="C123" t="n">
-        <v>117.96</v>
+        <v>44.87</v>
       </c>
       <c r="D123" t="n">
-        <v>24040</v>
+        <v>22823</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>113.24</v>
+        <v>44.83</v>
       </c>
       <c r="B124" t="n">
-        <v>24785</v>
+        <v>20767</v>
       </c>
       <c r="C124" t="n">
-        <v>114.78</v>
+        <v>50.9</v>
       </c>
       <c r="D124" t="n">
-        <v>22566</v>
+        <v>26460</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>93.54000000000001</v>
+        <v>45.39</v>
       </c>
       <c r="B125" t="n">
-        <v>29430</v>
+        <v>21576</v>
       </c>
       <c r="C125" t="n">
-        <v>93.97</v>
+        <v>56.42</v>
       </c>
       <c r="D125" t="n">
-        <v>24394</v>
+        <v>24415</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>90.01000000000001</v>
+        <v>45.49</v>
       </c>
       <c r="B126" t="n">
-        <v>24571</v>
+        <v>20824</v>
       </c>
       <c r="C126" t="n">
-        <v>90.04000000000001</v>
+        <v>42.63</v>
       </c>
       <c r="D126" t="n">
-        <v>16239</v>
+        <v>12904</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>99.27</v>
+        <v>46.26</v>
       </c>
       <c r="B127" t="n">
-        <v>42639</v>
+        <v>23106</v>
       </c>
       <c r="C127" t="n">
-        <v>103.67</v>
+        <v>45.77</v>
       </c>
       <c r="D127" t="n">
-        <v>28562</v>
+        <v>15209</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>111.71</v>
+        <v>47.05</v>
       </c>
       <c r="B128" t="n">
-        <v>29265</v>
+        <v>21461</v>
       </c>
       <c r="C128" t="n">
-        <v>107.63</v>
+        <v>42.21</v>
       </c>
       <c r="D128" t="n">
-        <v>27778</v>
+        <v>15932</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>97.97</v>
+        <v>47.9</v>
       </c>
       <c r="B129" t="n">
-        <v>41031</v>
+        <v>20693</v>
       </c>
       <c r="C129" t="n">
-        <v>101.4</v>
+        <v>51.96</v>
       </c>
       <c r="D129" t="n">
-        <v>29709</v>
+        <v>19088</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>24.4</v>
+        <v>48.07</v>
       </c>
       <c r="B130" t="n">
-        <v>24403</v>
+        <v>22710</v>
       </c>
       <c r="C130" t="n">
-        <v>26.09</v>
+        <v>53.71</v>
       </c>
       <c r="D130" t="n">
-        <v>12472</v>
+        <v>14420</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>99.23</v>
+        <v>48.19</v>
       </c>
       <c r="B131" t="n">
-        <v>42078</v>
+        <v>19763</v>
       </c>
       <c r="C131" t="n">
-        <v>98.64</v>
+        <v>42.73</v>
       </c>
       <c r="D131" t="n">
-        <v>25908</v>
+        <v>12659</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>91.09999999999999</v>
+        <v>48.83</v>
       </c>
       <c r="B132" t="n">
-        <v>22998</v>
+        <v>20196</v>
       </c>
       <c r="C132" t="n">
-        <v>88.40000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="D132" t="n">
-        <v>17376</v>
+        <v>23722</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>95.12</v>
+        <v>49.28</v>
       </c>
       <c r="B133" t="n">
-        <v>33594</v>
+        <v>19945</v>
       </c>
       <c r="C133" t="n">
-        <v>92.42</v>
+        <v>62.08</v>
       </c>
       <c r="D133" t="n">
-        <v>13982</v>
+        <v>15271</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>142.76</v>
+        <v>49.47</v>
       </c>
       <c r="B134" t="n">
-        <v>20842</v>
+        <v>23551</v>
       </c>
       <c r="C134" t="n">
-        <v>146.81</v>
+        <v>60.99</v>
       </c>
       <c r="D134" t="n">
-        <v>17255</v>
+        <v>23319</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>90.48</v>
+        <v>49.89</v>
       </c>
       <c r="B135" t="n">
-        <v>26442</v>
+        <v>20768</v>
       </c>
       <c r="C135" t="n">
-        <v>89.95999999999999</v>
+        <v>53.38</v>
       </c>
       <c r="D135" t="n">
-        <v>19063</v>
+        <v>16238</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>90.34</v>
+        <v>50.59</v>
       </c>
       <c r="B136" t="n">
-        <v>21820</v>
+        <v>21544</v>
       </c>
       <c r="C136" t="n">
-        <v>92.72</v>
+        <v>49.6</v>
       </c>
       <c r="D136" t="n">
-        <v>19695</v>
+        <v>27753</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>93.73999999999999</v>
+        <v>51.47</v>
       </c>
       <c r="B137" t="n">
-        <v>31915</v>
+        <v>20872</v>
       </c>
       <c r="C137" t="n">
-        <v>95.45999999999999</v>
+        <v>58.15</v>
       </c>
       <c r="D137" t="n">
-        <v>22744</v>
+        <v>13697</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>92.52</v>
+        <v>52</v>
       </c>
       <c r="B138" t="n">
-        <v>28893</v>
+        <v>20216</v>
       </c>
       <c r="C138" t="n">
-        <v>94.61</v>
+        <v>53.83</v>
       </c>
       <c r="D138" t="n">
-        <v>11778</v>
+        <v>19717</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>102.52</v>
+        <v>52.04</v>
       </c>
       <c r="B139" t="n">
-        <v>44282</v>
+        <v>19957</v>
       </c>
       <c r="C139" t="n">
-        <v>100.55</v>
+        <v>40.89</v>
       </c>
       <c r="D139" t="n">
-        <v>13703</v>
+        <v>29121</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>106.18</v>
+        <v>52.3</v>
       </c>
       <c r="B140" t="n">
-        <v>42628</v>
+        <v>21776</v>
       </c>
       <c r="C140" t="n">
-        <v>105.99</v>
+        <v>39.56</v>
       </c>
       <c r="D140" t="n">
-        <v>17471</v>
+        <v>22777</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>104.71</v>
+        <v>52.6</v>
       </c>
       <c r="B141" t="n">
-        <v>45290</v>
+        <v>20950</v>
       </c>
       <c r="C141" t="n">
-        <v>105.8</v>
+        <v>37.67</v>
       </c>
       <c r="D141" t="n">
-        <v>28740</v>
+        <v>28299</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>114.78</v>
+        <v>52.88</v>
       </c>
       <c r="B142" t="n">
-        <v>24090</v>
+        <v>22864</v>
       </c>
       <c r="C142" t="n">
-        <v>116.14</v>
+        <v>42.79</v>
       </c>
       <c r="D142" t="n">
-        <v>16022</v>
+        <v>14660</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>69.87</v>
+        <v>53.02</v>
       </c>
       <c r="B143" t="n">
-        <v>23470</v>
+        <v>20552</v>
       </c>
       <c r="C143" t="n">
-        <v>67.63</v>
+        <v>52.65</v>
       </c>
       <c r="D143" t="n">
-        <v>16335</v>
+        <v>13696</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>110.07</v>
+        <v>53.54</v>
       </c>
       <c r="B144" t="n">
-        <v>32895</v>
+        <v>23426</v>
       </c>
       <c r="C144" t="n">
-        <v>108.3</v>
+        <v>55.68</v>
       </c>
       <c r="D144" t="n">
-        <v>28199</v>
+        <v>25732</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>19.11</v>
+        <v>53.64</v>
       </c>
       <c r="B145" t="n">
-        <v>22295</v>
+        <v>20729</v>
       </c>
       <c r="C145" t="n">
-        <v>19.65</v>
+        <v>59.52</v>
       </c>
       <c r="D145" t="n">
-        <v>11053</v>
+        <v>12817</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>110.13</v>
+        <v>53.81</v>
       </c>
       <c r="B146" t="n">
-        <v>31708</v>
+        <v>20125</v>
       </c>
       <c r="C146" t="n">
-        <v>108.02</v>
+        <v>50</v>
       </c>
       <c r="D146" t="n">
-        <v>11949</v>
+        <v>21467</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>96.13</v>
+        <v>54.39</v>
       </c>
       <c r="B147" t="n">
-        <v>36579</v>
+        <v>20988</v>
       </c>
       <c r="C147" t="n">
-        <v>96.87</v>
+        <v>42.15</v>
       </c>
       <c r="D147" t="n">
-        <v>11037</v>
+        <v>28674</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>154.01</v>
+        <v>55.43</v>
       </c>
       <c r="B148" t="n">
-        <v>23452</v>
+        <v>20602</v>
       </c>
       <c r="C148" t="n">
-        <v>150.56</v>
+        <v>57.58</v>
       </c>
       <c r="D148" t="n">
-        <v>23390</v>
+        <v>20171</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>96.01000000000001</v>
+        <v>56.15</v>
       </c>
       <c r="B149" t="n">
-        <v>37051</v>
+        <v>21995</v>
       </c>
       <c r="C149" t="n">
-        <v>96.06</v>
+        <v>52.87</v>
       </c>
       <c r="D149" t="n">
-        <v>21600</v>
+        <v>10375</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>98.70999999999999</v>
+        <v>56.3</v>
       </c>
       <c r="B150" t="n">
-        <v>42136</v>
+        <v>22150</v>
       </c>
       <c r="C150" t="n">
-        <v>98.64</v>
+        <v>49.35</v>
       </c>
       <c r="D150" t="n">
-        <v>14056</v>
+        <v>27027</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>22.65</v>
+        <v>56.51</v>
       </c>
       <c r="B151" t="n">
-        <v>25744</v>
+        <v>20809</v>
       </c>
       <c r="C151" t="n">
-        <v>22.06</v>
+        <v>54.22</v>
       </c>
       <c r="D151" t="n">
-        <v>27355</v>
+        <v>27337</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>103.78</v>
+        <v>56.82</v>
       </c>
       <c r="B152" t="n">
-        <v>47582</v>
+        <v>20895</v>
       </c>
       <c r="C152" t="n">
-        <v>102.44</v>
+        <v>47.54</v>
       </c>
       <c r="D152" t="n">
-        <v>28040</v>
+        <v>26599</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>105.52</v>
+        <v>57.08</v>
       </c>
       <c r="B153" t="n">
-        <v>46119</v>
+        <v>21457</v>
       </c>
       <c r="C153" t="n">
-        <v>105.64</v>
+        <v>70.08</v>
       </c>
       <c r="D153" t="n">
-        <v>13884</v>
+        <v>20092</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>97.84</v>
+        <v>57.16</v>
       </c>
       <c r="B154" t="n">
-        <v>41180</v>
+        <v>20437</v>
       </c>
       <c r="C154" t="n">
-        <v>96.62</v>
+        <v>53.37</v>
       </c>
       <c r="D154" t="n">
-        <v>21932</v>
+        <v>15107</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>112.25</v>
+        <v>57.47</v>
       </c>
       <c r="B155" t="n">
-        <v>28805</v>
+        <v>19256</v>
       </c>
       <c r="C155" t="n">
-        <v>116.93</v>
+        <v>64.67</v>
       </c>
       <c r="D155" t="n">
-        <v>15276</v>
+        <v>23142</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>110.96</v>
+        <v>57.53</v>
       </c>
       <c r="B156" t="n">
-        <v>30462</v>
+        <v>19922</v>
       </c>
       <c r="C156" t="n">
-        <v>109.11</v>
+        <v>58.41</v>
       </c>
       <c r="D156" t="n">
-        <v>15680</v>
+        <v>13460</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>112.32</v>
+        <v>57.66</v>
       </c>
       <c r="B157" t="n">
-        <v>27194</v>
+        <v>22364</v>
       </c>
       <c r="C157" t="n">
-        <v>112.06</v>
+        <v>59.47</v>
       </c>
       <c r="D157" t="n">
-        <v>17252</v>
+        <v>21188</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>98.59</v>
+        <v>57.85</v>
       </c>
       <c r="B158" t="n">
-        <v>41862</v>
+        <v>21108</v>
       </c>
       <c r="C158" t="n">
-        <v>97.03</v>
+        <v>50.77</v>
       </c>
       <c r="D158" t="n">
-        <v>24025</v>
+        <v>26766</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>92.14</v>
+        <v>57.85</v>
       </c>
       <c r="B159" t="n">
-        <v>29253</v>
+        <v>21120</v>
       </c>
       <c r="C159" t="n">
-        <v>89.84999999999999</v>
+        <v>58.71</v>
       </c>
       <c r="D159" t="n">
-        <v>11353</v>
+        <v>24920</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>103.29</v>
+        <v>57.9</v>
       </c>
       <c r="B160" t="n">
-        <v>50583</v>
+        <v>21979</v>
       </c>
       <c r="C160" t="n">
-        <v>104.84</v>
+        <v>51.62</v>
       </c>
       <c r="D160" t="n">
-        <v>25231</v>
+        <v>26788</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>105.64</v>
+        <v>58.93</v>
       </c>
       <c r="B161" t="n">
-        <v>44886</v>
+        <v>22706</v>
       </c>
       <c r="C161" t="n">
-        <v>109.98</v>
+        <v>51.51</v>
       </c>
       <c r="D161" t="n">
-        <v>22868</v>
+        <v>14862</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>105.27</v>
+        <v>59.75</v>
       </c>
       <c r="B162" t="n">
-        <v>45507</v>
+        <v>20163</v>
       </c>
       <c r="C162" t="n">
-        <v>107.15</v>
+        <v>60.23</v>
       </c>
       <c r="D162" t="n">
-        <v>27765</v>
+        <v>10863</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>99.34999999999999</v>
+        <v>59.77</v>
       </c>
       <c r="B163" t="n">
-        <v>45108</v>
+        <v>20310</v>
       </c>
       <c r="C163" t="n">
-        <v>98.98999999999999</v>
+        <v>35.07</v>
       </c>
       <c r="D163" t="n">
-        <v>10369</v>
+        <v>12723</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>103.92</v>
+        <v>59.79</v>
       </c>
       <c r="B164" t="n">
-        <v>47685</v>
+        <v>21218</v>
       </c>
       <c r="C164" t="n">
-        <v>103.19</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D164" t="n">
-        <v>21600</v>
+        <v>19701</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>96.89</v>
+        <v>59.8</v>
       </c>
       <c r="B165" t="n">
-        <v>38374</v>
+        <v>20014</v>
       </c>
       <c r="C165" t="n">
-        <v>94.59</v>
+        <v>52.01</v>
       </c>
       <c r="D165" t="n">
-        <v>24032</v>
+        <v>28938</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>108.38</v>
+        <v>59.86</v>
       </c>
       <c r="B166" t="n">
-        <v>36711</v>
+        <v>21401</v>
       </c>
       <c r="C166" t="n">
-        <v>104.64</v>
+        <v>52.99</v>
       </c>
       <c r="D166" t="n">
-        <v>15253</v>
+        <v>29984</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>112.74</v>
+        <v>60.19</v>
       </c>
       <c r="B167" t="n">
-        <v>25802</v>
+        <v>20730</v>
       </c>
       <c r="C167" t="n">
-        <v>113.76</v>
+        <v>49.07</v>
       </c>
       <c r="D167" t="n">
-        <v>21783</v>
+        <v>27839</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>90.22</v>
+        <v>60.37</v>
       </c>
       <c r="B168" t="n">
-        <v>20327</v>
+        <v>20557</v>
       </c>
       <c r="C168" t="n">
-        <v>90.76000000000001</v>
+        <v>49.99</v>
       </c>
       <c r="D168" t="n">
-        <v>14850</v>
+        <v>19687</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>113.12</v>
+        <v>60.93</v>
       </c>
       <c r="B169" t="n">
-        <v>23297</v>
+        <v>19977</v>
       </c>
       <c r="C169" t="n">
-        <v>111.34</v>
+        <v>62.7</v>
       </c>
       <c r="D169" t="n">
-        <v>16447</v>
+        <v>15070</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>102.88</v>
+        <v>60.98</v>
       </c>
       <c r="B170" t="n">
-        <v>47322</v>
+        <v>20426</v>
       </c>
       <c r="C170" t="n">
-        <v>104.82</v>
+        <v>46.28</v>
       </c>
       <c r="D170" t="n">
-        <v>16594</v>
+        <v>26440</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>102.26</v>
+        <v>61.18</v>
       </c>
       <c r="B171" t="n">
-        <v>47368</v>
+        <v>20491</v>
       </c>
       <c r="C171" t="n">
-        <v>104.75</v>
+        <v>47.09</v>
       </c>
       <c r="D171" t="n">
-        <v>16850</v>
+        <v>27330</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>96.45</v>
+        <v>61.85</v>
       </c>
       <c r="B172" t="n">
-        <v>36787</v>
+        <v>21946</v>
       </c>
       <c r="C172" t="n">
-        <v>95.11</v>
+        <v>69.58</v>
       </c>
       <c r="D172" t="n">
-        <v>13296</v>
+        <v>16827</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>172.21</v>
+        <v>62.37</v>
       </c>
       <c r="B173" t="n">
-        <v>23447</v>
+        <v>20867</v>
       </c>
       <c r="C173" t="n">
-        <v>174.37</v>
+        <v>59.86</v>
       </c>
       <c r="D173" t="n">
-        <v>11954</v>
+        <v>15343</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>100.63</v>
+        <v>62.72</v>
       </c>
       <c r="B174" t="n">
-        <v>46547</v>
+        <v>20167</v>
       </c>
       <c r="C174" t="n">
-        <v>101.18</v>
+        <v>69.25</v>
       </c>
       <c r="D174" t="n">
-        <v>22083</v>
+        <v>29231</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>92.54000000000001</v>
+        <v>62.72</v>
       </c>
       <c r="B175" t="n">
-        <v>25343</v>
+        <v>20541</v>
       </c>
       <c r="C175" t="n">
-        <v>93.48</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="D175" t="n">
-        <v>18286</v>
+        <v>28906</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>71.97</v>
+        <v>62.96</v>
       </c>
       <c r="B176" t="n">
-        <v>22592</v>
+        <v>21450</v>
       </c>
       <c r="C176" t="n">
-        <v>73.86</v>
+        <v>60.75</v>
       </c>
       <c r="D176" t="n">
-        <v>11687</v>
+        <v>10524</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>177.81</v>
+        <v>63.37</v>
       </c>
       <c r="B177" t="n">
-        <v>22039</v>
+        <v>21733</v>
       </c>
       <c r="C177" t="n">
-        <v>173.72</v>
+        <v>62.35</v>
       </c>
       <c r="D177" t="n">
-        <v>26444</v>
+        <v>25406</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>107.91</v>
+        <v>63.67</v>
       </c>
       <c r="B178" t="n">
-        <v>40042</v>
+        <v>21793</v>
       </c>
       <c r="C178" t="n">
-        <v>108.35</v>
+        <v>48.63</v>
       </c>
       <c r="D178" t="n">
-        <v>28051</v>
+        <v>19790</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>111.59</v>
+        <v>64.2</v>
       </c>
       <c r="B179" t="n">
-        <v>27124</v>
+        <v>20508</v>
       </c>
       <c r="C179" t="n">
-        <v>116.15</v>
+        <v>69.34</v>
       </c>
       <c r="D179" t="n">
-        <v>24366</v>
+        <v>25190</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>113.55</v>
+        <v>64.37</v>
       </c>
       <c r="B180" t="n">
-        <v>25770</v>
+        <v>19969</v>
       </c>
       <c r="C180" t="n">
-        <v>116.94</v>
+        <v>66.38</v>
       </c>
       <c r="D180" t="n">
-        <v>17739</v>
+        <v>20861</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>98.73999999999999</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="B181" t="n">
-        <v>44034</v>
+        <v>21258</v>
       </c>
       <c r="C181" t="n">
-        <v>99.44</v>
+        <v>65.95</v>
       </c>
       <c r="D181" t="n">
-        <v>26696</v>
+        <v>24636</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>99.79000000000001</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="B182" t="n">
-        <v>41956</v>
+        <v>20771</v>
       </c>
       <c r="C182" t="n">
-        <v>103.91</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="D182" t="n">
-        <v>13353</v>
+        <v>20880</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>100.34</v>
+        <v>65.78</v>
       </c>
       <c r="B183" t="n">
-        <v>40894</v>
+        <v>19661</v>
       </c>
       <c r="C183" t="n">
-        <v>100.2</v>
+        <v>66.19</v>
       </c>
       <c r="D183" t="n">
-        <v>16354</v>
+        <v>29958</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>101.72</v>
+        <v>66.02</v>
       </c>
       <c r="B184" t="n">
-        <v>43788</v>
+        <v>20797</v>
       </c>
       <c r="C184" t="n">
-        <v>101.67</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="D184" t="n">
-        <v>12247</v>
+        <v>20105</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>95.65000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="B185" t="n">
-        <v>33970</v>
+        <v>20317</v>
       </c>
       <c r="C185" t="n">
-        <v>96.51000000000001</v>
+        <v>65.59</v>
       </c>
       <c r="D185" t="n">
-        <v>24620</v>
+        <v>16446</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>102.62</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="B186" t="n">
-        <v>47601</v>
+        <v>21274</v>
       </c>
       <c r="C186" t="n">
-        <v>103.6</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="D186" t="n">
-        <v>14761</v>
+        <v>10668</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1.64</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="B187" t="n">
-        <v>24484</v>
+        <v>22964</v>
       </c>
       <c r="C187" t="n">
-        <v>1.67</v>
+        <v>60.22</v>
       </c>
       <c r="D187" t="n">
-        <v>12493</v>
+        <v>14456</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>105.87</v>
+        <v>67.87</v>
       </c>
       <c r="B188" t="n">
-        <v>42916</v>
+        <v>20582</v>
       </c>
       <c r="C188" t="n">
-        <v>107.2</v>
+        <v>73.98</v>
       </c>
       <c r="D188" t="n">
-        <v>13555</v>
+        <v>26337</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>107.52</v>
+        <v>67.92</v>
       </c>
       <c r="B189" t="n">
-        <v>40635</v>
+        <v>20138</v>
       </c>
       <c r="C189" t="n">
-        <v>108.12</v>
+        <v>88.05</v>
       </c>
       <c r="D189" t="n">
-        <v>26446</v>
+        <v>28084</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>101.72</v>
+        <v>68.11</v>
       </c>
       <c r="B190" t="n">
-        <v>47803</v>
+        <v>21013</v>
       </c>
       <c r="C190" t="n">
-        <v>99.55</v>
+        <v>57.11</v>
       </c>
       <c r="D190" t="n">
-        <v>14544</v>
+        <v>26729</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>112.42</v>
+        <v>68.22</v>
       </c>
       <c r="B191" t="n">
-        <v>24377</v>
+        <v>18860</v>
       </c>
       <c r="C191" t="n">
-        <v>112.58</v>
+        <v>59.92</v>
       </c>
       <c r="D191" t="n">
-        <v>29682</v>
+        <v>25666</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>97.54000000000001</v>
+        <v>68.37</v>
       </c>
       <c r="B192" t="n">
-        <v>42113</v>
+        <v>20751</v>
       </c>
       <c r="C192" t="n">
-        <v>99.14</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="D192" t="n">
-        <v>22362</v>
+        <v>27256</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>107.3</v>
+        <v>68.41</v>
       </c>
       <c r="B193" t="n">
-        <v>42439</v>
+        <v>20101</v>
       </c>
       <c r="C193" t="n">
-        <v>103.94</v>
+        <v>84.19</v>
       </c>
       <c r="D193" t="n">
-        <v>19678</v>
+        <v>25062</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>90.14</v>
+        <v>69.52</v>
       </c>
       <c r="B194" t="n">
-        <v>25108</v>
+        <v>19787</v>
       </c>
       <c r="C194" t="n">
-        <v>88.19</v>
+        <v>66.48</v>
       </c>
       <c r="D194" t="n">
-        <v>14398</v>
+        <v>16910</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>83.98999999999999</v>
+        <v>69.78</v>
       </c>
       <c r="B195" t="n">
-        <v>25420</v>
+        <v>20573</v>
       </c>
       <c r="C195" t="n">
-        <v>80.45</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="D195" t="n">
-        <v>11331</v>
+        <v>14373</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>111.32</v>
+        <v>70.8</v>
       </c>
       <c r="B196" t="n">
-        <v>31614</v>
+        <v>19792</v>
       </c>
       <c r="C196" t="n">
-        <v>110.28</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="D196" t="n">
-        <v>13907</v>
+        <v>17822</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>96.18000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="B197" t="n">
-        <v>35803</v>
+        <v>20707</v>
       </c>
       <c r="C197" t="n">
-        <v>98.8</v>
+        <v>78.28</v>
       </c>
       <c r="D197" t="n">
-        <v>10743</v>
+        <v>21099</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>90.26000000000001</v>
+        <v>70.91</v>
       </c>
       <c r="B198" t="n">
-        <v>24808</v>
+        <v>20174</v>
       </c>
       <c r="C198" t="n">
-        <v>92.58</v>
+        <v>74.25</v>
       </c>
       <c r="D198" t="n">
-        <v>19808</v>
+        <v>21839</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>90.5</v>
+        <v>70.92</v>
       </c>
       <c r="B199" t="n">
-        <v>24424</v>
+        <v>20987</v>
       </c>
       <c r="C199" t="n">
-        <v>87.78</v>
+        <v>62.29</v>
       </c>
       <c r="D199" t="n">
-        <v>23473</v>
+        <v>12028</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>98.65000000000001</v>
+        <v>71.94</v>
       </c>
       <c r="B200" t="n">
-        <v>44259</v>
+        <v>20820</v>
       </c>
       <c r="C200" t="n">
-        <v>99.76000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="D200" t="n">
-        <v>12557</v>
+        <v>16328</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>93.88</v>
+        <v>72.62</v>
       </c>
       <c r="B201" t="n">
-        <v>28818</v>
+        <v>21596</v>
       </c>
       <c r="C201" t="n">
-        <v>96.29000000000001</v>
+        <v>68.25</v>
       </c>
       <c r="D201" t="n">
-        <v>25344</v>
+        <v>20868</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>155.42</v>
+        <v>72.94</v>
       </c>
       <c r="B202" t="n">
-        <v>23179</v>
+        <v>19881</v>
       </c>
       <c r="C202" t="n">
-        <v>154.05</v>
+        <v>58.7</v>
       </c>
       <c r="D202" t="n">
-        <v>19885</v>
+        <v>28241</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>39.87</v>
+        <v>73.45</v>
       </c>
       <c r="B203" t="n">
-        <v>24675</v>
+        <v>20652</v>
       </c>
       <c r="C203" t="n">
-        <v>40.53</v>
+        <v>66.5</v>
       </c>
       <c r="D203" t="n">
-        <v>22371</v>
+        <v>28631</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>110</v>
+        <v>73.8</v>
       </c>
       <c r="B204" t="n">
-        <v>33364</v>
+        <v>19861</v>
       </c>
       <c r="C204" t="n">
-        <v>111.89</v>
+        <v>64.75</v>
       </c>
       <c r="D204" t="n">
-        <v>26760</v>
+        <v>21204</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>107.15</v>
+        <v>73.89</v>
       </c>
       <c r="B205" t="n">
-        <v>44174</v>
+        <v>21432</v>
       </c>
       <c r="C205" t="n">
-        <v>109.07</v>
+        <v>90.83</v>
       </c>
       <c r="D205" t="n">
-        <v>10806</v>
+        <v>12801</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>104.68</v>
+        <v>74.06</v>
       </c>
       <c r="B206" t="n">
-        <v>44236</v>
+        <v>21767</v>
       </c>
       <c r="C206" t="n">
-        <v>100.46</v>
+        <v>85.91</v>
       </c>
       <c r="D206" t="n">
-        <v>12306</v>
+        <v>29662</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>112.14</v>
+        <v>74.22</v>
       </c>
       <c r="B207" t="n">
-        <v>26750</v>
+        <v>20563</v>
       </c>
       <c r="C207" t="n">
-        <v>109.63</v>
+        <v>70.92</v>
       </c>
       <c r="D207" t="n">
-        <v>18612</v>
+        <v>21942</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>102.96</v>
+        <v>74.27</v>
       </c>
       <c r="B208" t="n">
-        <v>47748</v>
+        <v>21483</v>
       </c>
       <c r="C208" t="n">
-        <v>101.19</v>
+        <v>84.45</v>
       </c>
       <c r="D208" t="n">
-        <v>16652</v>
+        <v>15776</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>74.73999999999999</v>
+        <v>74.44</v>
       </c>
       <c r="B209" t="n">
-        <v>25729</v>
+        <v>19702</v>
       </c>
       <c r="C209" t="n">
-        <v>76.98</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="D209" t="n">
-        <v>25675</v>
+        <v>28439</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>43.93</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="B210" t="n">
-        <v>23888</v>
+        <v>20236</v>
       </c>
       <c r="C210" t="n">
-        <v>43.78</v>
+        <v>61.76</v>
       </c>
       <c r="D210" t="n">
-        <v>13965</v>
+        <v>27121</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>95.13</v>
+        <v>74.88</v>
       </c>
       <c r="B211" t="n">
-        <v>32957</v>
+        <v>20559</v>
       </c>
       <c r="C211" t="n">
-        <v>95.31999999999999</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="D211" t="n">
-        <v>20717</v>
+        <v>21335</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>100.64</v>
+        <v>75.55</v>
       </c>
       <c r="B212" t="n">
-        <v>45273</v>
+        <v>21083</v>
       </c>
       <c r="C212" t="n">
-        <v>101.94</v>
+        <v>80.58</v>
       </c>
       <c r="D212" t="n">
-        <v>18432</v>
+        <v>22711</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>90.06999999999999</v>
+        <v>75.63</v>
       </c>
       <c r="B213" t="n">
-        <v>24326</v>
+        <v>21046</v>
       </c>
       <c r="C213" t="n">
-        <v>87.23</v>
+        <v>105.68</v>
       </c>
       <c r="D213" t="n">
-        <v>17082</v>
+        <v>26184</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>100.89</v>
+        <v>75.72</v>
       </c>
       <c r="B214" t="n">
-        <v>44301</v>
+        <v>21313</v>
       </c>
       <c r="C214" t="n">
-        <v>101.88</v>
+        <v>97.08</v>
       </c>
       <c r="D214" t="n">
-        <v>19827</v>
+        <v>28240</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>107.49</v>
+        <v>76.36</v>
       </c>
       <c r="B215" t="n">
-        <v>38389</v>
+        <v>20684</v>
       </c>
       <c r="C215" t="n">
-        <v>111.76</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="D215" t="n">
-        <v>20061</v>
+        <v>12820</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>161.07</v>
+        <v>77.05</v>
       </c>
       <c r="B216" t="n">
-        <v>23189</v>
+        <v>20323</v>
       </c>
       <c r="C216" t="n">
-        <v>166.61</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="D216" t="n">
-        <v>23375</v>
+        <v>20414</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>114.64</v>
+        <v>77.06</v>
       </c>
       <c r="B217" t="n">
-        <v>22796</v>
+        <v>20417</v>
       </c>
       <c r="C217" t="n">
-        <v>119.44</v>
+        <v>78.97</v>
       </c>
       <c r="D217" t="n">
-        <v>16982</v>
+        <v>23923</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>60.63</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="B218" t="n">
-        <v>23421</v>
+        <v>20190</v>
       </c>
       <c r="C218" t="n">
-        <v>58.69</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D218" t="n">
-        <v>24663</v>
+        <v>11738</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>90.94</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="B219" t="n">
-        <v>25807</v>
+        <v>20140</v>
       </c>
       <c r="C219" t="n">
-        <v>89.68000000000001</v>
+        <v>90.25</v>
       </c>
       <c r="D219" t="n">
-        <v>18595</v>
+        <v>21356</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>110.28</v>
+        <v>78.75</v>
       </c>
       <c r="B220" t="n">
-        <v>29899</v>
+        <v>19511</v>
       </c>
       <c r="C220" t="n">
-        <v>108.37</v>
+        <v>101.35</v>
       </c>
       <c r="D220" t="n">
-        <v>14045</v>
+        <v>24356</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>104.9</v>
+        <v>79.14</v>
       </c>
       <c r="B221" t="n">
-        <v>46412</v>
+        <v>21679</v>
       </c>
       <c r="C221" t="n">
-        <v>100.13</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="D221" t="n">
-        <v>25875</v>
+        <v>11051</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>108.7</v>
+        <v>79.25</v>
       </c>
       <c r="B222" t="n">
-        <v>37337</v>
+        <v>20188</v>
       </c>
       <c r="C222" t="n">
-        <v>109.35</v>
+        <v>56.33</v>
       </c>
       <c r="D222" t="n">
-        <v>16220</v>
+        <v>19988</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>98.83</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="B223" t="n">
-        <v>42143</v>
+        <v>20617</v>
       </c>
       <c r="C223" t="n">
-        <v>97.7</v>
+        <v>87.44</v>
       </c>
       <c r="D223" t="n">
-        <v>19298</v>
+        <v>12585</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>93.20999999999999</v>
+        <v>79.48</v>
       </c>
       <c r="B224" t="n">
-        <v>29750</v>
+        <v>19833</v>
       </c>
       <c r="C224" t="n">
-        <v>96.92</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="D224" t="n">
-        <v>12888</v>
+        <v>27221</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>95.70999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="B225" t="n">
-        <v>34164</v>
+        <v>19817</v>
       </c>
       <c r="C225" t="n">
-        <v>94.51000000000001</v>
+        <v>99</v>
       </c>
       <c r="D225" t="n">
-        <v>22688</v>
+        <v>10218</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>90.56999999999999</v>
+        <v>80.78</v>
       </c>
       <c r="B226" t="n">
-        <v>25226</v>
+        <v>19405</v>
       </c>
       <c r="C226" t="n">
-        <v>92.23999999999999</v>
+        <v>84.17</v>
       </c>
       <c r="D226" t="n">
-        <v>23573</v>
+        <v>23456</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>106.14</v>
+        <v>81.38</v>
       </c>
       <c r="B227" t="n">
-        <v>45270</v>
+        <v>19734</v>
       </c>
       <c r="C227" t="n">
-        <v>108.59</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="D227" t="n">
-        <v>13473</v>
+        <v>13734</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>112.13</v>
+        <v>82.02</v>
       </c>
       <c r="B228" t="n">
-        <v>27254</v>
+        <v>20973</v>
       </c>
       <c r="C228" t="n">
-        <v>108.16</v>
+        <v>79.94</v>
       </c>
       <c r="D228" t="n">
-        <v>15168</v>
+        <v>13894</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>109.87</v>
+        <v>82.2</v>
       </c>
       <c r="B229" t="n">
-        <v>33492</v>
+        <v>19697</v>
       </c>
       <c r="C229" t="n">
-        <v>113.6</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="D229" t="n">
-        <v>17411</v>
+        <v>15199</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>21.92</v>
+        <v>82.75</v>
       </c>
       <c r="B230" t="n">
-        <v>22074</v>
+        <v>20119</v>
       </c>
       <c r="C230" t="n">
-        <v>21.16</v>
+        <v>83.95</v>
       </c>
       <c r="D230" t="n">
-        <v>17871</v>
+        <v>17634</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>97.11</v>
+        <v>83.55</v>
       </c>
       <c r="B231" t="n">
-        <v>40113</v>
+        <v>20867</v>
       </c>
       <c r="C231" t="n">
-        <v>93.05</v>
+        <v>76.69</v>
       </c>
       <c r="D231" t="n">
-        <v>28451</v>
+        <v>23867</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>101.94</v>
+        <v>83.94</v>
       </c>
       <c r="B232" t="n">
-        <v>45269</v>
+        <v>20000</v>
       </c>
       <c r="C232" t="n">
-        <v>98.28</v>
+        <v>66.17</v>
       </c>
       <c r="D232" t="n">
-        <v>15279</v>
+        <v>27645</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>108</v>
+        <v>84.33</v>
       </c>
       <c r="B233" t="n">
-        <v>40200</v>
+        <v>20821</v>
       </c>
       <c r="C233" t="n">
-        <v>109.3</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="D233" t="n">
-        <v>17676</v>
+        <v>26416</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>98.7</v>
+        <v>84.69</v>
       </c>
       <c r="B234" t="n">
-        <v>44994</v>
+        <v>20996</v>
       </c>
       <c r="C234" t="n">
-        <v>100.5</v>
+        <v>81.13</v>
       </c>
       <c r="D234" t="n">
-        <v>11074</v>
+        <v>26694</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>108.86</v>
+        <v>84.69</v>
       </c>
       <c r="B235" t="n">
-        <v>39020</v>
+        <v>20963</v>
       </c>
       <c r="C235" t="n">
-        <v>109.73</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="D235" t="n">
-        <v>19864</v>
+        <v>27871</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>108.87</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="B236" t="n">
-        <v>37584</v>
+        <v>20337</v>
       </c>
       <c r="C236" t="n">
-        <v>110.08</v>
+        <v>87.23</v>
       </c>
       <c r="D236" t="n">
-        <v>17950</v>
+        <v>27829</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>102.61</v>
+        <v>84.92</v>
       </c>
       <c r="B237" t="n">
-        <v>47907</v>
+        <v>21117</v>
       </c>
       <c r="C237" t="n">
-        <v>98.48999999999999</v>
+        <v>91.06</v>
       </c>
       <c r="D237" t="n">
-        <v>11788</v>
+        <v>28295</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>98.43000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="B238" t="n">
-        <v>40002</v>
+        <v>20361</v>
       </c>
       <c r="C238" t="n">
-        <v>96.67</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="D238" t="n">
-        <v>22065</v>
+        <v>16032</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>94.5</v>
+        <v>85.23</v>
       </c>
       <c r="B239" t="n">
-        <v>32170</v>
+        <v>20149</v>
       </c>
       <c r="C239" t="n">
-        <v>93.98</v>
+        <v>67</v>
       </c>
       <c r="D239" t="n">
-        <v>12319</v>
+        <v>21208</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>139.62</v>
+        <v>85.64</v>
       </c>
       <c r="B240" t="n">
-        <v>23011</v>
+        <v>20344</v>
       </c>
       <c r="C240" t="n">
-        <v>143.48</v>
+        <v>97.56</v>
       </c>
       <c r="D240" t="n">
-        <v>23174</v>
+        <v>28253</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>104.62</v>
+        <v>86.44</v>
       </c>
       <c r="B241" t="n">
-        <v>45956</v>
+        <v>20484</v>
       </c>
       <c r="C241" t="n">
-        <v>108.39</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="D241" t="n">
-        <v>13055</v>
+        <v>25991</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>92.51000000000001</v>
+        <v>86.67</v>
       </c>
       <c r="B242" t="n">
-        <v>30827</v>
+        <v>19471</v>
       </c>
       <c r="C242" t="n">
-        <v>90.97</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="D242" t="n">
-        <v>10529</v>
+        <v>18456</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>55.67</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="B243" t="n">
-        <v>23075</v>
+        <v>20326</v>
       </c>
       <c r="C243" t="n">
-        <v>58.61</v>
+        <v>88</v>
       </c>
       <c r="D243" t="n">
-        <v>17726</v>
+        <v>13173</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>105.88</v>
+        <v>86.78</v>
       </c>
       <c r="B244" t="n">
-        <v>44625</v>
+        <v>19845</v>
       </c>
       <c r="C244" t="n">
-        <v>108.96</v>
+        <v>96.64</v>
       </c>
       <c r="D244" t="n">
-        <v>23873</v>
+        <v>19487</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>114.97</v>
+        <v>87.12</v>
       </c>
       <c r="B245" t="n">
-        <v>24039</v>
+        <v>19936</v>
       </c>
       <c r="C245" t="n">
-        <v>119.43</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="D245" t="n">
-        <v>20219</v>
+        <v>19501</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>114.01</v>
+        <v>87.37</v>
       </c>
       <c r="B246" t="n">
-        <v>24969</v>
+        <v>20018</v>
       </c>
       <c r="C246" t="n">
-        <v>116.08</v>
+        <v>84.58</v>
       </c>
       <c r="D246" t="n">
-        <v>19026</v>
+        <v>21277</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>26.84</v>
+        <v>88.37</v>
       </c>
       <c r="B247" t="n">
-        <v>22893</v>
+        <v>19854</v>
       </c>
       <c r="C247" t="n">
-        <v>26.21</v>
+        <v>96.12</v>
       </c>
       <c r="D247" t="n">
-        <v>25853</v>
+        <v>25647</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>106.32</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="B248" t="n">
-        <v>46016</v>
+        <v>20842</v>
       </c>
       <c r="C248" t="n">
-        <v>108.84</v>
+        <v>96.45</v>
       </c>
       <c r="D248" t="n">
-        <v>14240</v>
+        <v>19372</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>93.36</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="B249" t="n">
-        <v>28110</v>
+        <v>20606</v>
       </c>
       <c r="C249" t="n">
-        <v>95.98999999999999</v>
+        <v>61.85</v>
       </c>
       <c r="D249" t="n">
-        <v>11868</v>
+        <v>21801</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>98.67</v>
+        <v>88.63</v>
       </c>
       <c r="B250" t="n">
-        <v>42963</v>
+        <v>20994</v>
       </c>
       <c r="C250" t="n">
-        <v>95.72</v>
+        <v>80.89</v>
       </c>
       <c r="D250" t="n">
-        <v>29426</v>
+        <v>27273</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>91.22</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="B251" t="n">
-        <v>25797</v>
+        <v>20464</v>
       </c>
       <c r="C251" t="n">
-        <v>94.94</v>
+        <v>105.8</v>
       </c>
       <c r="D251" t="n">
-        <v>14497</v>
+        <v>23572</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>91.40000000000001</v>
+        <v>88.95</v>
       </c>
       <c r="B252" t="n">
-        <v>23652</v>
+        <v>20572</v>
       </c>
       <c r="C252" t="n">
-        <v>90.79000000000001</v>
+        <v>98.16</v>
       </c>
       <c r="D252" t="n">
-        <v>19336</v>
+        <v>10182</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>105.25</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="B253" t="n">
-        <v>44347</v>
+        <v>20856</v>
       </c>
       <c r="C253" t="n">
-        <v>107.84</v>
+        <v>78.61</v>
       </c>
       <c r="D253" t="n">
-        <v>19086</v>
+        <v>11137</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>6.86</v>
+        <v>89.53</v>
       </c>
       <c r="B254" t="n">
-        <v>22576</v>
+        <v>21621</v>
       </c>
       <c r="C254" t="n">
-        <v>6.93</v>
+        <v>110.35</v>
       </c>
       <c r="D254" t="n">
-        <v>10618</v>
+        <v>28469</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>113.1</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="B255" t="n">
-        <v>26025</v>
+        <v>21198</v>
       </c>
       <c r="C255" t="n">
-        <v>111.09</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D255" t="n">
-        <v>17946</v>
+        <v>19959</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>135.93</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="B256" t="n">
-        <v>22182</v>
+        <v>21933</v>
       </c>
       <c r="C256" t="n">
-        <v>134.11</v>
+        <v>103.32</v>
       </c>
       <c r="D256" t="n">
-        <v>24895</v>
+        <v>20484</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>107.6</v>
+        <v>90.67</v>
       </c>
       <c r="B257" t="n">
-        <v>40070</v>
+        <v>21420</v>
       </c>
       <c r="C257" t="n">
-        <v>111.33</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="D257" t="n">
-        <v>21856</v>
+        <v>18804</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>132.72</v>
+        <v>90.84</v>
       </c>
       <c r="B258" t="n">
-        <v>23515</v>
+        <v>21390</v>
       </c>
       <c r="C258" t="n">
-        <v>136.36</v>
+        <v>118.54</v>
       </c>
       <c r="D258" t="n">
-        <v>11662</v>
+        <v>17504</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>106.05</v>
+        <v>90.87</v>
       </c>
       <c r="B259" t="n">
-        <v>47027</v>
+        <v>20708</v>
       </c>
       <c r="C259" t="n">
-        <v>105.07</v>
+        <v>105.75</v>
       </c>
       <c r="D259" t="n">
-        <v>26620</v>
+        <v>15316</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>104.67</v>
+        <v>91.53</v>
       </c>
       <c r="B260" t="n">
-        <v>47161</v>
+        <v>21023</v>
       </c>
       <c r="C260" t="n">
-        <v>103.25</v>
+        <v>88.2</v>
       </c>
       <c r="D260" t="n">
-        <v>17274</v>
+        <v>15166</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>97.90000000000001</v>
+        <v>91.78</v>
       </c>
       <c r="B261" t="n">
-        <v>41534</v>
+        <v>22799</v>
       </c>
       <c r="C261" t="n">
-        <v>95.34999999999999</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="D261" t="n">
-        <v>11418</v>
+        <v>11071</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>108.77</v>
+        <v>92.02</v>
       </c>
       <c r="B262" t="n">
-        <v>37344</v>
+        <v>22973</v>
       </c>
       <c r="C262" t="n">
-        <v>111.41</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="D262" t="n">
-        <v>26674</v>
+        <v>27971</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>94.61</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="B263" t="n">
-        <v>32740</v>
+        <v>22313</v>
       </c>
       <c r="C263" t="n">
-        <v>90.95</v>
+        <v>84.73</v>
       </c>
       <c r="D263" t="n">
-        <v>18081</v>
+        <v>27292</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>113.39</v>
+        <v>92.63</v>
       </c>
       <c r="B264" t="n">
-        <v>25945</v>
+        <v>21872</v>
       </c>
       <c r="C264" t="n">
-        <v>117.53</v>
+        <v>85.42</v>
       </c>
       <c r="D264" t="n">
-        <v>28056</v>
+        <v>21807</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>101.83</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="B265" t="n">
-        <v>49046</v>
+        <v>23415</v>
       </c>
       <c r="C265" t="n">
-        <v>104.92</v>
+        <v>97.7</v>
       </c>
       <c r="D265" t="n">
-        <v>20424</v>
+        <v>23149</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>113.53</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="B266" t="n">
-        <v>23194</v>
+        <v>22011</v>
       </c>
       <c r="C266" t="n">
-        <v>116.04</v>
+        <v>105.92</v>
       </c>
       <c r="D266" t="n">
-        <v>12307</v>
+        <v>29066</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>98.34999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="B267" t="n">
-        <v>41094</v>
+        <v>23177</v>
       </c>
       <c r="C267" t="n">
-        <v>97.83</v>
+        <v>117.18</v>
       </c>
       <c r="D267" t="n">
-        <v>18425</v>
+        <v>20589</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>103.29</v>
+        <v>93.63</v>
       </c>
       <c r="B268" t="n">
-        <v>46376</v>
+        <v>23521</v>
       </c>
       <c r="C268" t="n">
-        <v>100.03</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="D268" t="n">
-        <v>12873</v>
+        <v>17886</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>98.25</v>
+        <v>94.69</v>
       </c>
       <c r="B269" t="n">
-        <v>44270</v>
+        <v>25287</v>
       </c>
       <c r="C269" t="n">
-        <v>100.88</v>
+        <v>93.61</v>
       </c>
       <c r="D269" t="n">
-        <v>26745</v>
+        <v>25731</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>104.01</v>
+        <v>95.03</v>
       </c>
       <c r="B270" t="n">
-        <v>47220</v>
+        <v>24473</v>
       </c>
       <c r="C270" t="n">
-        <v>106.77</v>
+        <v>106.2</v>
       </c>
       <c r="D270" t="n">
-        <v>16171</v>
+        <v>12074</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>113.63</v>
+        <v>95.38</v>
       </c>
       <c r="B271" t="n">
-        <v>23666</v>
+        <v>25577</v>
       </c>
       <c r="C271" t="n">
-        <v>114.34</v>
+        <v>110.49</v>
       </c>
       <c r="D271" t="n">
-        <v>19075</v>
+        <v>15164</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>101.68</v>
+        <v>95.67</v>
       </c>
       <c r="B272" t="n">
-        <v>46230</v>
+        <v>26757</v>
       </c>
       <c r="C272" t="n">
-        <v>101.83</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="D272" t="n">
-        <v>13779</v>
+        <v>27044</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>91.16</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="B273" t="n">
-        <v>26739</v>
+        <v>26459</v>
       </c>
       <c r="C273" t="n">
-        <v>91.52</v>
+        <v>105.38</v>
       </c>
       <c r="D273" t="n">
-        <v>25299</v>
+        <v>20847</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>91.33</v>
+        <v>95.7</v>
       </c>
       <c r="B274" t="n">
-        <v>26535</v>
+        <v>26197</v>
       </c>
       <c r="C274" t="n">
-        <v>93.42</v>
+        <v>99.69</v>
       </c>
       <c r="D274" t="n">
-        <v>21972</v>
+        <v>12943</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>112.06</v>
+        <v>95.84</v>
       </c>
       <c r="B275" t="n">
-        <v>27015</v>
+        <v>25838</v>
       </c>
       <c r="C275" t="n">
-        <v>110.32</v>
+        <v>100.91</v>
       </c>
       <c r="D275" t="n">
-        <v>15967</v>
+        <v>25624</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>63.54</v>
+        <v>95.97</v>
       </c>
       <c r="B276" t="n">
-        <v>22818</v>
+        <v>26590</v>
       </c>
       <c r="C276" t="n">
-        <v>63.8</v>
+        <v>85.3</v>
       </c>
       <c r="D276" t="n">
-        <v>15510</v>
+        <v>25372</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>111.6</v>
+        <v>96.28</v>
       </c>
       <c r="B277" t="n">
-        <v>28985</v>
+        <v>27218</v>
       </c>
       <c r="C277" t="n">
-        <v>108.04</v>
+        <v>111.76</v>
       </c>
       <c r="D277" t="n">
-        <v>24710</v>
+        <v>29867</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>110.95</v>
+        <v>97.11</v>
       </c>
       <c r="B278" t="n">
-        <v>28590</v>
+        <v>27989</v>
       </c>
       <c r="C278" t="n">
-        <v>108.04</v>
+        <v>86.89</v>
       </c>
       <c r="D278" t="n">
-        <v>10541</v>
+        <v>21611</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>101.09</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="B279" t="n">
-        <v>46029</v>
+        <v>28816</v>
       </c>
       <c r="C279" t="n">
-        <v>103.21</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="D279" t="n">
-        <v>16338</v>
+        <v>24253</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>97.56</v>
+        <v>97.39</v>
       </c>
       <c r="B280" t="n">
-        <v>36892</v>
+        <v>29770</v>
       </c>
       <c r="C280" t="n">
-        <v>99.93000000000001</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="D280" t="n">
-        <v>21449</v>
+        <v>15764</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>100.42</v>
+        <v>97.44</v>
       </c>
       <c r="B281" t="n">
-        <v>45678</v>
+        <v>29751</v>
       </c>
       <c r="C281" t="n">
-        <v>97.76000000000001</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="D281" t="n">
-        <v>25521</v>
+        <v>17019</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>112.12</v>
+        <v>97.91</v>
       </c>
       <c r="B282" t="n">
-        <v>25306</v>
+        <v>30846</v>
       </c>
       <c r="C282" t="n">
-        <v>113</v>
+        <v>88.27</v>
       </c>
       <c r="D282" t="n">
-        <v>14573</v>
+        <v>29925</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>96.52</v>
+        <v>98.44</v>
       </c>
       <c r="B283" t="n">
-        <v>36942</v>
+        <v>31038</v>
       </c>
       <c r="C283" t="n">
-        <v>94.29000000000001</v>
+        <v>112.3</v>
       </c>
       <c r="D283" t="n">
-        <v>20585</v>
+        <v>21214</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>40.48</v>
+        <v>100.15</v>
       </c>
       <c r="B284" t="n">
-        <v>23190</v>
+        <v>35540</v>
       </c>
       <c r="C284" t="n">
-        <v>38.81</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="D284" t="n">
-        <v>12010</v>
+        <v>25348</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>106.11</v>
+        <v>100.42</v>
       </c>
       <c r="B285" t="n">
-        <v>40996</v>
+        <v>35382</v>
       </c>
       <c r="C285" t="n">
-        <v>102.5</v>
+        <v>104.43</v>
       </c>
       <c r="D285" t="n">
-        <v>19137</v>
+        <v>10292</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>110.5</v>
+        <v>100.87</v>
       </c>
       <c r="B286" t="n">
-        <v>32347</v>
+        <v>35899</v>
       </c>
       <c r="C286" t="n">
-        <v>107.08</v>
+        <v>102.9</v>
       </c>
       <c r="D286" t="n">
-        <v>13801</v>
+        <v>12380</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>100.68</v>
+        <v>101.57</v>
       </c>
       <c r="B287" t="n">
-        <v>46394</v>
+        <v>37788</v>
       </c>
       <c r="C287" t="n">
-        <v>101.11</v>
+        <v>120.82</v>
       </c>
       <c r="D287" t="n">
-        <v>18958</v>
+        <v>28298</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>112.53</v>
+        <v>101.66</v>
       </c>
       <c r="B288" t="n">
-        <v>27956</v>
+        <v>36360</v>
       </c>
       <c r="C288" t="n">
-        <v>115.02</v>
+        <v>103.55</v>
       </c>
       <c r="D288" t="n">
-        <v>29517</v>
+        <v>21975</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>108.05</v>
+        <v>101.91</v>
       </c>
       <c r="B289" t="n">
-        <v>39429</v>
+        <v>37096</v>
       </c>
       <c r="C289" t="n">
-        <v>104.38</v>
+        <v>97.05</v>
       </c>
       <c r="D289" t="n">
-        <v>15392</v>
+        <v>10842</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>123.3</v>
+        <v>102.31</v>
       </c>
       <c r="B290" t="n">
-        <v>21623</v>
+        <v>36744</v>
       </c>
       <c r="C290" t="n">
-        <v>124.26</v>
+        <v>100.51</v>
       </c>
       <c r="D290" t="n">
-        <v>18988</v>
+        <v>19954</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>112.4</v>
+        <v>102.62</v>
       </c>
       <c r="B291" t="n">
-        <v>26731</v>
+        <v>37871</v>
       </c>
       <c r="C291" t="n">
-        <v>112.35</v>
+        <v>100.63</v>
       </c>
       <c r="D291" t="n">
-        <v>25762</v>
+        <v>25029</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>93.08</v>
+        <v>102.76</v>
       </c>
       <c r="B292" t="n">
-        <v>27368</v>
+        <v>37699</v>
       </c>
       <c r="C292" t="n">
-        <v>96.17</v>
+        <v>108.9</v>
       </c>
       <c r="D292" t="n">
-        <v>27500</v>
+        <v>17545</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>103.95</v>
+        <v>103.6</v>
       </c>
       <c r="B293" t="n">
-        <v>47404</v>
+        <v>38109</v>
       </c>
       <c r="C293" t="n">
-        <v>100.54</v>
+        <v>121.62</v>
       </c>
       <c r="D293" t="n">
-        <v>20599</v>
+        <v>24222</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>108.88</v>
+        <v>104.2</v>
       </c>
       <c r="B294" t="n">
-        <v>35813</v>
+        <v>38695</v>
       </c>
       <c r="C294" t="n">
-        <v>105.86</v>
+        <v>112.19</v>
       </c>
       <c r="D294" t="n">
-        <v>19030</v>
+        <v>14829</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>109.04</v>
+        <v>104.3</v>
       </c>
       <c r="B295" t="n">
-        <v>37420</v>
+        <v>37578</v>
       </c>
       <c r="C295" t="n">
-        <v>111.03</v>
+        <v>102.78</v>
       </c>
       <c r="D295" t="n">
-        <v>26147</v>
+        <v>22177</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>71.91</v>
+        <v>104.36</v>
       </c>
       <c r="B296" t="n">
-        <v>24347</v>
+        <v>38278</v>
       </c>
       <c r="C296" t="n">
-        <v>71.68000000000001</v>
+        <v>126.06</v>
       </c>
       <c r="D296" t="n">
-        <v>22873</v>
+        <v>17191</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>109.3</v>
+        <v>104.66</v>
       </c>
       <c r="B297" t="n">
-        <v>34648</v>
+        <v>37158</v>
       </c>
       <c r="C297" t="n">
-        <v>111.43</v>
+        <v>110.11</v>
       </c>
       <c r="D297" t="n">
-        <v>12099</v>
+        <v>17279</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>146.19</v>
+        <v>105.67</v>
       </c>
       <c r="B298" t="n">
-        <v>24286</v>
+        <v>35252</v>
       </c>
       <c r="C298" t="n">
-        <v>146.56</v>
+        <v>100.38</v>
       </c>
       <c r="D298" t="n">
-        <v>10130</v>
+        <v>29614</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>110.02</v>
+        <v>105.76</v>
       </c>
       <c r="B299" t="n">
-        <v>32132</v>
+        <v>35121</v>
       </c>
       <c r="C299" t="n">
-        <v>113.56</v>
+        <v>109.41</v>
       </c>
       <c r="D299" t="n">
-        <v>26413</v>
+        <v>24925</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>97.94</v>
+        <v>105.94</v>
       </c>
       <c r="B300" t="n">
-        <v>40509</v>
+        <v>35282</v>
       </c>
       <c r="C300" t="n">
-        <v>100.45</v>
+        <v>116.61</v>
       </c>
       <c r="D300" t="n">
-        <v>14133</v>
+        <v>13888</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>106.87</v>
+        <v>106.43</v>
       </c>
       <c r="B301" t="n">
-        <v>41726</v>
+        <v>33824</v>
       </c>
       <c r="C301" t="n">
-        <v>106.37</v>
+        <v>81.61</v>
       </c>
       <c r="D301" t="n">
-        <v>24711</v>
+        <v>12979</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>44.34</v>
+        <v>106.53</v>
       </c>
       <c r="B302" t="n">
-        <v>24918</v>
+        <v>34974</v>
       </c>
       <c r="C302" t="n">
-        <v>44.4</v>
+        <v>111.5</v>
       </c>
       <c r="D302" t="n">
-        <v>29349</v>
+        <v>19951</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>96.61</v>
+        <v>106.53</v>
       </c>
       <c r="B303" t="n">
-        <v>41090</v>
+        <v>33636</v>
       </c>
       <c r="C303" t="n">
-        <v>98.45999999999999</v>
+        <v>106.67</v>
       </c>
       <c r="D303" t="n">
-        <v>11845</v>
+        <v>24203</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>108.07</v>
+        <v>106.62</v>
       </c>
       <c r="B304" t="n">
-        <v>38149</v>
+        <v>33352</v>
       </c>
       <c r="C304" t="n">
-        <v>107.87</v>
+        <v>119.19</v>
       </c>
       <c r="D304" t="n">
-        <v>24550</v>
+        <v>16515</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>95.44</v>
+        <v>108.34</v>
       </c>
       <c r="B305" t="n">
-        <v>36243</v>
+        <v>30587</v>
       </c>
       <c r="C305" t="n">
-        <v>96.88</v>
+        <v>130.3</v>
       </c>
       <c r="D305" t="n">
-        <v>20439</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>103.25</v>
+        <v>108.6</v>
       </c>
       <c r="B306" t="n">
-        <v>47286</v>
+        <v>29441</v>
       </c>
       <c r="C306" t="n">
-        <v>100.42</v>
+        <v>119.57</v>
       </c>
       <c r="D306" t="n">
-        <v>10125</v>
+        <v>29420</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>107.9</v>
+        <v>108.78</v>
       </c>
       <c r="B307" t="n">
-        <v>41728</v>
+        <v>28901</v>
       </c>
       <c r="C307" t="n">
-        <v>104.32</v>
+        <v>125.32</v>
       </c>
       <c r="D307" t="n">
-        <v>16214</v>
+        <v>25860</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>138.24</v>
+        <v>108.79</v>
       </c>
       <c r="B308" t="n">
-        <v>21422</v>
+        <v>29802</v>
       </c>
       <c r="C308" t="n">
-        <v>142.34</v>
+        <v>84.11</v>
       </c>
       <c r="D308" t="n">
-        <v>11295</v>
+        <v>14402</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>40.5</v>
+        <v>108.83</v>
       </c>
       <c r="B309" t="n">
-        <v>25842</v>
+        <v>28692</v>
       </c>
       <c r="C309" t="n">
-        <v>42.03</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="D309" t="n">
-        <v>18314</v>
+        <v>25446</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>105.17</v>
+        <v>108.95</v>
       </c>
       <c r="B310" t="n">
-        <v>44228</v>
+        <v>28714</v>
       </c>
       <c r="C310" t="n">
-        <v>104.52</v>
+        <v>115.14</v>
       </c>
       <c r="D310" t="n">
-        <v>10063</v>
+        <v>10805</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>112.4</v>
+        <v>108.97</v>
       </c>
       <c r="B311" t="n">
-        <v>25726</v>
+        <v>27861</v>
       </c>
       <c r="C311" t="n">
-        <v>108.3</v>
+        <v>117.21</v>
       </c>
       <c r="D311" t="n">
-        <v>17816</v>
+        <v>19009</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>93.19</v>
+        <v>109.43</v>
       </c>
       <c r="B312" t="n">
-        <v>27857</v>
+        <v>28889</v>
       </c>
       <c r="C312" t="n">
-        <v>90.98</v>
+        <v>90.37</v>
       </c>
       <c r="D312" t="n">
-        <v>20032</v>
+        <v>17626</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>107.25</v>
+        <v>109.45</v>
       </c>
       <c r="B313" t="n">
-        <v>41873</v>
+        <v>28290</v>
       </c>
       <c r="C313" t="n">
-        <v>109.91</v>
+        <v>117.15</v>
       </c>
       <c r="D313" t="n">
-        <v>28760</v>
+        <v>29335</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>107.88</v>
+        <v>109.48</v>
       </c>
       <c r="B314" t="n">
-        <v>39171</v>
+        <v>27621</v>
       </c>
       <c r="C314" t="n">
-        <v>108.19</v>
+        <v>115.18</v>
       </c>
       <c r="D314" t="n">
-        <v>17646</v>
+        <v>26603</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>102.22</v>
+        <v>109.73</v>
       </c>
       <c r="B315" t="n">
-        <v>47105</v>
+        <v>27145</v>
       </c>
       <c r="C315" t="n">
-        <v>104.47</v>
+        <v>88.75</v>
       </c>
       <c r="D315" t="n">
-        <v>23646</v>
+        <v>19464</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>16.06</v>
+        <v>110.43</v>
       </c>
       <c r="B316" t="n">
-        <v>24256</v>
+        <v>25474</v>
       </c>
       <c r="C316" t="n">
-        <v>15</v>
+        <v>129.07</v>
       </c>
       <c r="D316" t="n">
-        <v>17398</v>
+        <v>16263</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>100.71</v>
+        <v>110.56</v>
       </c>
       <c r="B317" t="n">
-        <v>45284</v>
+        <v>24726</v>
       </c>
       <c r="C317" t="n">
-        <v>101.42</v>
+        <v>110.67</v>
       </c>
       <c r="D317" t="n">
-        <v>16769</v>
+        <v>28660</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>98.95999999999999</v>
+        <v>110.62</v>
       </c>
       <c r="B318" t="n">
-        <v>43513</v>
+        <v>24880</v>
       </c>
       <c r="C318" t="n">
-        <v>99.95</v>
+        <v>137.23</v>
       </c>
       <c r="D318" t="n">
-        <v>10072</v>
+        <v>22581</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>93.22</v>
+        <v>110.98</v>
       </c>
       <c r="B319" t="n">
-        <v>27802</v>
+        <v>24617</v>
       </c>
       <c r="C319" t="n">
-        <v>93.29000000000001</v>
+        <v>115.79</v>
       </c>
       <c r="D319" t="n">
-        <v>15915</v>
+        <v>12251</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>105.57</v>
+        <v>111.27</v>
       </c>
       <c r="B320" t="n">
-        <v>46162</v>
+        <v>24579</v>
       </c>
       <c r="C320" t="n">
-        <v>107.57</v>
+        <v>135.84</v>
       </c>
       <c r="D320" t="n">
-        <v>24094</v>
+        <v>15862</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>111.61</v>
+        <v>111.37</v>
       </c>
       <c r="B321" t="n">
-        <v>27840</v>
+        <v>25816</v>
       </c>
       <c r="C321" t="n">
-        <v>109.8</v>
+        <v>99.14</v>
       </c>
       <c r="D321" t="n">
-        <v>16706</v>
+        <v>26275</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>90.66</v>
+        <v>112.3</v>
       </c>
       <c r="B322" t="n">
-        <v>24962</v>
+        <v>23144</v>
       </c>
       <c r="C322" t="n">
-        <v>90.79000000000001</v>
+        <v>86.81</v>
       </c>
       <c r="D322" t="n">
-        <v>28999</v>
+        <v>22130</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>106.8</v>
+        <v>112.88</v>
       </c>
       <c r="B323" t="n">
-        <v>43591</v>
+        <v>22901</v>
       </c>
       <c r="C323" t="n">
-        <v>104.58</v>
+        <v>138.06</v>
       </c>
       <c r="D323" t="n">
-        <v>10350</v>
+        <v>21505</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>106.05</v>
+        <v>113.07</v>
       </c>
       <c r="B324" t="n">
-        <v>44026</v>
+        <v>21610</v>
       </c>
       <c r="C324" t="n">
-        <v>106.33</v>
+        <v>123.7</v>
       </c>
       <c r="D324" t="n">
-        <v>19503</v>
+        <v>24645</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>114.82</v>
+        <v>114.11</v>
       </c>
       <c r="B325" t="n">
-        <v>21461</v>
+        <v>20164</v>
       </c>
       <c r="C325" t="n">
-        <v>116.6</v>
+        <v>91.28</v>
       </c>
       <c r="D325" t="n">
-        <v>16300</v>
+        <v>23705</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>111.24</v>
+        <v>114.27</v>
       </c>
       <c r="B326" t="n">
-        <v>28597</v>
+        <v>22408</v>
       </c>
       <c r="C326" t="n">
-        <v>110.89</v>
+        <v>136.36</v>
       </c>
       <c r="D326" t="n">
-        <v>15184</v>
+        <v>16987</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>106.05</v>
+        <v>114.57</v>
       </c>
       <c r="B327" t="n">
-        <v>44144</v>
+        <v>21660</v>
       </c>
       <c r="C327" t="n">
-        <v>105.13</v>
+        <v>111.6</v>
       </c>
       <c r="D327" t="n">
-        <v>24341</v>
+        <v>16176</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>39.52</v>
+        <v>114.85</v>
       </c>
       <c r="B328" t="n">
-        <v>23258</v>
+        <v>21808</v>
       </c>
       <c r="C328" t="n">
-        <v>38.91</v>
+        <v>101.42</v>
       </c>
       <c r="D328" t="n">
-        <v>17599</v>
+        <v>25411</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>100.67</v>
+        <v>115.19</v>
       </c>
       <c r="B329" t="n">
-        <v>44738</v>
+        <v>20318</v>
       </c>
       <c r="C329" t="n">
-        <v>99.01000000000001</v>
+        <v>98.78</v>
       </c>
       <c r="D329" t="n">
-        <v>17434</v>
+        <v>14353</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>118.44</v>
+        <v>115.36</v>
       </c>
       <c r="B330" t="n">
-        <v>23098</v>
+        <v>19982</v>
       </c>
       <c r="C330" t="n">
-        <v>121.15</v>
+        <v>136.13</v>
       </c>
       <c r="D330" t="n">
-        <v>22697</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>91.02</v>
+        <v>115.67</v>
       </c>
       <c r="B331" t="n">
-        <v>23495</v>
+        <v>21724</v>
       </c>
       <c r="C331" t="n">
-        <v>88.20999999999999</v>
+        <v>130.88</v>
       </c>
       <c r="D331" t="n">
-        <v>15239</v>
+        <v>17704</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>102.96</v>
+        <v>115.93</v>
       </c>
       <c r="B332" t="n">
-        <v>49067</v>
+        <v>19057</v>
       </c>
       <c r="C332" t="n">
-        <v>102.01</v>
+        <v>87.84</v>
       </c>
       <c r="D332" t="n">
-        <v>19152</v>
+        <v>21722</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>103.22</v>
+        <v>117.02</v>
       </c>
       <c r="B333" t="n">
-        <v>46228</v>
+        <v>20290</v>
       </c>
       <c r="C333" t="n">
-        <v>106.46</v>
+        <v>116.1</v>
       </c>
       <c r="D333" t="n">
-        <v>19044</v>
+        <v>16446</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>107.93</v>
+        <v>117.22</v>
       </c>
       <c r="B334" t="n">
-        <v>38075</v>
+        <v>20499</v>
       </c>
       <c r="C334" t="n">
-        <v>112.23</v>
+        <v>114.28</v>
       </c>
       <c r="D334" t="n">
-        <v>28224</v>
+        <v>20320</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>101.91</v>
+        <v>117.52</v>
       </c>
       <c r="B335" t="n">
-        <v>44568</v>
+        <v>21967</v>
       </c>
       <c r="C335" t="n">
-        <v>98.26000000000001</v>
+        <v>109.63</v>
       </c>
       <c r="D335" t="n">
-        <v>24817</v>
+        <v>16119</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>98.52</v>
+        <v>117.53</v>
       </c>
       <c r="B336" t="n">
-        <v>41410</v>
+        <v>18877</v>
       </c>
       <c r="C336" t="n">
-        <v>94.73999999999999</v>
+        <v>124.28</v>
       </c>
       <c r="D336" t="n">
-        <v>16179</v>
+        <v>11065</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>113.53</v>
+        <v>117.89</v>
       </c>
       <c r="B337" t="n">
-        <v>23061</v>
+        <v>20738</v>
       </c>
       <c r="C337" t="n">
-        <v>109.67</v>
+        <v>101.64</v>
       </c>
       <c r="D337" t="n">
-        <v>10894</v>
+        <v>20316</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>138.1</v>
+        <v>118.09</v>
       </c>
       <c r="B338" t="n">
-        <v>23818</v>
+        <v>19244</v>
       </c>
       <c r="C338" t="n">
-        <v>141.08</v>
+        <v>92.58</v>
       </c>
       <c r="D338" t="n">
-        <v>12531</v>
+        <v>27197</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>99.2</v>
+        <v>119.05</v>
       </c>
       <c r="B339" t="n">
-        <v>43055</v>
+        <v>18650</v>
       </c>
       <c r="C339" t="n">
-        <v>99.81</v>
+        <v>135.91</v>
       </c>
       <c r="D339" t="n">
-        <v>23217</v>
+        <v>19041</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>104.09</v>
+        <v>119.15</v>
       </c>
       <c r="B340" t="n">
-        <v>46828</v>
+        <v>20390</v>
       </c>
       <c r="C340" t="n">
-        <v>101.68</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D340" t="n">
-        <v>28285</v>
+        <v>15386</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>103.25</v>
+        <v>119.32</v>
       </c>
       <c r="B341" t="n">
-        <v>45230</v>
+        <v>18702</v>
       </c>
       <c r="C341" t="n">
-        <v>103.93</v>
+        <v>142.37</v>
       </c>
       <c r="D341" t="n">
-        <v>11706</v>
+        <v>12644</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>111.15</v>
+        <v>119.41</v>
       </c>
       <c r="B342" t="n">
-        <v>29859</v>
+        <v>17705</v>
       </c>
       <c r="C342" t="n">
-        <v>111.96</v>
+        <v>99.03</v>
       </c>
       <c r="D342" t="n">
-        <v>13335</v>
+        <v>22465</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>178.62</v>
+        <v>120.43</v>
       </c>
       <c r="B343" t="n">
-        <v>24354</v>
+        <v>20012</v>
       </c>
       <c r="C343" t="n">
-        <v>180</v>
+        <v>116.45</v>
       </c>
       <c r="D343" t="n">
-        <v>18643</v>
+        <v>18194</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>113.57</v>
+        <v>120.43</v>
       </c>
       <c r="B344" t="n">
-        <v>24782</v>
+        <v>18951</v>
       </c>
       <c r="C344" t="n">
-        <v>113.33</v>
+        <v>107.87</v>
       </c>
       <c r="D344" t="n">
-        <v>12117</v>
+        <v>24984</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>93.34999999999999</v>
+        <v>121.58</v>
       </c>
       <c r="B345" t="n">
-        <v>27522</v>
+        <v>18471</v>
       </c>
       <c r="C345" t="n">
-        <v>97.04000000000001</v>
+        <v>111.72</v>
       </c>
       <c r="D345" t="n">
-        <v>16450</v>
+        <v>19118</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>62.55</v>
+        <v>121.62</v>
       </c>
       <c r="B346" t="n">
-        <v>23289</v>
+        <v>20771</v>
       </c>
       <c r="C346" t="n">
-        <v>63.59</v>
+        <v>114.92</v>
       </c>
       <c r="D346" t="n">
-        <v>14315</v>
+        <v>29444</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>142.19</v>
+        <v>122.05</v>
       </c>
       <c r="B347" t="n">
-        <v>22797</v>
+        <v>20074</v>
       </c>
       <c r="C347" t="n">
-        <v>141.48</v>
+        <v>101.98</v>
       </c>
       <c r="D347" t="n">
-        <v>10227</v>
+        <v>13344</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>112.62</v>
+        <v>122.92</v>
       </c>
       <c r="B348" t="n">
-        <v>23963</v>
+        <v>19216</v>
       </c>
       <c r="C348" t="n">
-        <v>115.89</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="D348" t="n">
-        <v>10354</v>
+        <v>28132</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>96.28</v>
+        <v>123.43</v>
       </c>
       <c r="B349" t="n">
-        <v>37230</v>
+        <v>20992</v>
       </c>
       <c r="C349" t="n">
-        <v>96.41</v>
+        <v>135.11</v>
       </c>
       <c r="D349" t="n">
-        <v>21951</v>
+        <v>12279</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>104.84</v>
+        <v>123.46</v>
       </c>
       <c r="B350" t="n">
-        <v>45515</v>
+        <v>20628</v>
       </c>
       <c r="C350" t="n">
-        <v>103.91</v>
+        <v>149.09</v>
       </c>
       <c r="D350" t="n">
-        <v>29101</v>
+        <v>27093</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>98.37</v>
+        <v>123.53</v>
       </c>
       <c r="B351" t="n">
-        <v>43053</v>
+        <v>20093</v>
       </c>
       <c r="C351" t="n">
-        <v>96.5</v>
+        <v>114.26</v>
       </c>
       <c r="D351" t="n">
-        <v>13855</v>
+        <v>26149</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>103.99</v>
+        <v>123.81</v>
       </c>
       <c r="B352" t="n">
-        <v>47340</v>
+        <v>22592</v>
       </c>
       <c r="C352" t="n">
-        <v>101.28</v>
+        <v>138.03</v>
       </c>
       <c r="D352" t="n">
-        <v>18664</v>
+        <v>13121</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>112.5</v>
+        <v>124.25</v>
       </c>
       <c r="B353" t="n">
-        <v>25632</v>
+        <v>17877</v>
       </c>
       <c r="C353" t="n">
-        <v>115.36</v>
+        <v>117.18</v>
       </c>
       <c r="D353" t="n">
-        <v>16201</v>
+        <v>14617</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>111.76</v>
+        <v>124.31</v>
       </c>
       <c r="B354" t="n">
-        <v>29644</v>
+        <v>18071</v>
       </c>
       <c r="C354" t="n">
-        <v>113.55</v>
+        <v>111.92</v>
       </c>
       <c r="D354" t="n">
-        <v>17863</v>
+        <v>12492</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>31.94</v>
+        <v>124.63</v>
       </c>
       <c r="B355" t="n">
-        <v>25222</v>
+        <v>18999</v>
       </c>
       <c r="C355" t="n">
-        <v>33.24</v>
+        <v>113.6</v>
       </c>
       <c r="D355" t="n">
-        <v>11300</v>
+        <v>16825</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>94.06999999999999</v>
+        <v>124.78</v>
       </c>
       <c r="B356" t="n">
-        <v>31709</v>
+        <v>16194</v>
       </c>
       <c r="C356" t="n">
-        <v>97.19</v>
+        <v>102.24</v>
       </c>
       <c r="D356" t="n">
-        <v>11480</v>
+        <v>15797</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>103.32</v>
+        <v>124.93</v>
       </c>
       <c r="B357" t="n">
-        <v>45372</v>
+        <v>21289</v>
       </c>
       <c r="C357" t="n">
-        <v>99.7</v>
+        <v>114.33</v>
       </c>
       <c r="D357" t="n">
-        <v>10794</v>
+        <v>20482</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>97.65000000000001</v>
+        <v>125.46</v>
       </c>
       <c r="B358" t="n">
-        <v>39005</v>
+        <v>18503</v>
       </c>
       <c r="C358" t="n">
-        <v>96.84</v>
+        <v>145.03</v>
       </c>
       <c r="D358" t="n">
-        <v>14682</v>
+        <v>19369</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>118.99</v>
+        <v>125.8</v>
       </c>
       <c r="B359" t="n">
-        <v>23125</v>
+        <v>18709</v>
       </c>
       <c r="C359" t="n">
-        <v>120.68</v>
+        <v>125.9</v>
       </c>
       <c r="D359" t="n">
-        <v>12688</v>
+        <v>21937</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>149.36</v>
+        <v>126.04</v>
       </c>
       <c r="B360" t="n">
-        <v>25378</v>
+        <v>19987</v>
       </c>
       <c r="C360" t="n">
-        <v>148.69</v>
+        <v>112.76</v>
       </c>
       <c r="D360" t="n">
-        <v>16287</v>
+        <v>12843</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>108.15</v>
+        <v>126.19</v>
       </c>
       <c r="B361" t="n">
-        <v>37684</v>
+        <v>19910</v>
       </c>
       <c r="C361" t="n">
-        <v>106.84</v>
+        <v>125.54</v>
       </c>
       <c r="D361" t="n">
-        <v>18680</v>
+        <v>18514</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>102.11</v>
+        <v>126.47</v>
       </c>
       <c r="B362" t="n">
-        <v>46345</v>
+        <v>18639</v>
       </c>
       <c r="C362" t="n">
-        <v>100.29</v>
+        <v>132.35</v>
       </c>
       <c r="D362" t="n">
-        <v>10398</v>
+        <v>26332</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>94.64</v>
+        <v>126.9</v>
       </c>
       <c r="B363" t="n">
-        <v>34108</v>
+        <v>21743</v>
       </c>
       <c r="C363" t="n">
-        <v>98.16</v>
+        <v>137.19</v>
       </c>
       <c r="D363" t="n">
-        <v>25000</v>
+        <v>16206</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>97.37</v>
+        <v>126.9</v>
       </c>
       <c r="B364" t="n">
-        <v>39783</v>
+        <v>21131</v>
       </c>
       <c r="C364" t="n">
-        <v>97.94</v>
+        <v>115</v>
       </c>
       <c r="D364" t="n">
-        <v>17823</v>
+        <v>29344</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>85.04000000000001</v>
+        <v>127.11</v>
       </c>
       <c r="B365" t="n">
-        <v>23468</v>
+        <v>20749</v>
       </c>
       <c r="C365" t="n">
-        <v>87.51000000000001</v>
+        <v>119.02</v>
       </c>
       <c r="D365" t="n">
-        <v>15492</v>
+        <v>24338</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>107.44</v>
+        <v>127.13</v>
       </c>
       <c r="B366" t="n">
-        <v>37317</v>
+        <v>19727</v>
       </c>
       <c r="C366" t="n">
-        <v>104.7</v>
+        <v>131.98</v>
       </c>
       <c r="D366" t="n">
-        <v>20034</v>
+        <v>22957</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>93.44</v>
+        <v>127.47</v>
       </c>
       <c r="B367" t="n">
-        <v>31434</v>
+        <v>20939</v>
       </c>
       <c r="C367" t="n">
-        <v>89.63</v>
+        <v>109.92</v>
       </c>
       <c r="D367" t="n">
-        <v>23148</v>
+        <v>16735</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>108.91</v>
+        <v>128.95</v>
       </c>
       <c r="B368" t="n">
-        <v>38369</v>
+        <v>19562</v>
       </c>
       <c r="C368" t="n">
-        <v>109.01</v>
+        <v>122.18</v>
       </c>
       <c r="D368" t="n">
-        <v>27246</v>
+        <v>24843</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>90.97</v>
+        <v>129.05</v>
       </c>
       <c r="B369" t="n">
-        <v>26440</v>
+        <v>18478</v>
       </c>
       <c r="C369" t="n">
-        <v>91.87</v>
+        <v>119.5</v>
       </c>
       <c r="D369" t="n">
-        <v>16122</v>
+        <v>11050</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>131.47</v>
+        <v>129.43</v>
       </c>
       <c r="B370" t="n">
-        <v>22713</v>
+        <v>19038</v>
       </c>
       <c r="C370" t="n">
-        <v>132.73</v>
+        <v>142.61</v>
       </c>
       <c r="D370" t="n">
-        <v>10393</v>
+        <v>11769</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>9.51</v>
+        <v>129.91</v>
       </c>
       <c r="B371" t="n">
-        <v>25384</v>
+        <v>19465</v>
       </c>
       <c r="C371" t="n">
-        <v>9.42</v>
+        <v>119.37</v>
       </c>
       <c r="D371" t="n">
-        <v>17049</v>
+        <v>26415</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>96.43000000000001</v>
+        <v>130.1</v>
       </c>
       <c r="B372" t="n">
-        <v>39300</v>
+        <v>19505</v>
       </c>
       <c r="C372" t="n">
-        <v>92.76000000000001</v>
+        <v>140.83</v>
       </c>
       <c r="D372" t="n">
-        <v>25337</v>
+        <v>17590</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>91.34</v>
+        <v>130.75</v>
       </c>
       <c r="B373" t="n">
-        <v>26152</v>
+        <v>21780</v>
       </c>
       <c r="C373" t="n">
-        <v>91.68000000000001</v>
+        <v>126.41</v>
       </c>
       <c r="D373" t="n">
-        <v>10863</v>
+        <v>26258</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>114.54</v>
+        <v>130.83</v>
       </c>
       <c r="B374" t="n">
-        <v>23376</v>
+        <v>19944</v>
       </c>
       <c r="C374" t="n">
-        <v>115.74</v>
+        <v>146.9</v>
       </c>
       <c r="D374" t="n">
-        <v>11343</v>
+        <v>18512</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>104.56</v>
+        <v>132.26</v>
       </c>
       <c r="B375" t="n">
-        <v>45823</v>
+        <v>19693</v>
       </c>
       <c r="C375" t="n">
-        <v>104.15</v>
+        <v>153.39</v>
       </c>
       <c r="D375" t="n">
-        <v>20119</v>
+        <v>28257</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>108.08</v>
+        <v>132.45</v>
       </c>
       <c r="B376" t="n">
-        <v>40433</v>
+        <v>18443</v>
       </c>
       <c r="C376" t="n">
-        <v>110.32</v>
+        <v>156.35</v>
       </c>
       <c r="D376" t="n">
-        <v>11485</v>
+        <v>21757</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>114.1</v>
+        <v>133.59</v>
       </c>
       <c r="B377" t="n">
-        <v>24277</v>
+        <v>21105</v>
       </c>
       <c r="C377" t="n">
-        <v>112.1</v>
+        <v>132.44</v>
       </c>
       <c r="D377" t="n">
-        <v>20243</v>
+        <v>21402</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>67.89</v>
+        <v>133.91</v>
       </c>
       <c r="B378" t="n">
-        <v>25403</v>
+        <v>22096</v>
       </c>
       <c r="C378" t="n">
-        <v>65.53</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="D378" t="n">
-        <v>17040</v>
+        <v>23012</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>12.96</v>
+        <v>134.56</v>
       </c>
       <c r="B379" t="n">
-        <v>23276</v>
+        <v>19833</v>
       </c>
       <c r="C379" t="n">
-        <v>13.02</v>
+        <v>128.17</v>
       </c>
       <c r="D379" t="n">
-        <v>28681</v>
+        <v>13673</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>113.83</v>
+        <v>134.8</v>
       </c>
       <c r="B380" t="n">
-        <v>26346</v>
+        <v>20458</v>
       </c>
       <c r="C380" t="n">
-        <v>118.15</v>
+        <v>142</v>
       </c>
       <c r="D380" t="n">
-        <v>10831</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>112.19</v>
+        <v>135.13</v>
       </c>
       <c r="B381" t="n">
-        <v>29705</v>
+        <v>21974</v>
       </c>
       <c r="C381" t="n">
-        <v>108.69</v>
+        <v>158.15</v>
       </c>
       <c r="D381" t="n">
-        <v>15610</v>
+        <v>21954</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>94.52</v>
+        <v>135.14</v>
       </c>
       <c r="B382" t="n">
-        <v>32112</v>
+        <v>18417</v>
       </c>
       <c r="C382" t="n">
-        <v>95.05</v>
+        <v>137.55</v>
       </c>
       <c r="D382" t="n">
-        <v>25978</v>
+        <v>20656</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>95.73</v>
+        <v>135.16</v>
       </c>
       <c r="B383" t="n">
-        <v>34455</v>
+        <v>17913</v>
       </c>
       <c r="C383" t="n">
-        <v>97.37</v>
+        <v>119.7</v>
       </c>
       <c r="D383" t="n">
-        <v>27719</v>
+        <v>16981</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>107.41</v>
+        <v>135.34</v>
       </c>
       <c r="B384" t="n">
-        <v>40477</v>
+        <v>17950</v>
       </c>
       <c r="C384" t="n">
-        <v>110.53</v>
+        <v>121.98</v>
       </c>
       <c r="D384" t="n">
-        <v>28946</v>
+        <v>24047</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>111.65</v>
+        <v>135.36</v>
       </c>
       <c r="B385" t="n">
-        <v>26589</v>
+        <v>20238</v>
       </c>
       <c r="C385" t="n">
-        <v>114.38</v>
+        <v>117.73</v>
       </c>
       <c r="D385" t="n">
-        <v>15894</v>
+        <v>17543</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>96.11</v>
+        <v>135.56</v>
       </c>
       <c r="B386" t="n">
-        <v>37778</v>
+        <v>18861</v>
       </c>
       <c r="C386" t="n">
-        <v>98.40000000000001</v>
+        <v>107.43</v>
       </c>
       <c r="D386" t="n">
-        <v>29854</v>
+        <v>12325</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>20.63</v>
+        <v>135.69</v>
       </c>
       <c r="B387" t="n">
-        <v>25032</v>
+        <v>20076</v>
       </c>
       <c r="C387" t="n">
-        <v>19.48</v>
+        <v>145.14</v>
       </c>
       <c r="D387" t="n">
-        <v>28991</v>
+        <v>17070</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>131.94</v>
+        <v>136.5</v>
       </c>
       <c r="B388" t="n">
-        <v>21403</v>
+        <v>20894</v>
       </c>
       <c r="C388" t="n">
-        <v>135.9</v>
+        <v>157.66</v>
       </c>
       <c r="D388" t="n">
-        <v>29152</v>
+        <v>16480</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>78.67</v>
+        <v>136.61</v>
       </c>
       <c r="B389" t="n">
-        <v>23392</v>
+        <v>20495</v>
       </c>
       <c r="C389" t="n">
-        <v>76.72</v>
+        <v>151.53</v>
       </c>
       <c r="D389" t="n">
-        <v>18992</v>
+        <v>12125</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>92.06</v>
+        <v>136.98</v>
       </c>
       <c r="B390" t="n">
-        <v>24235</v>
+        <v>18767</v>
       </c>
       <c r="C390" t="n">
-        <v>90.09</v>
+        <v>134.46</v>
       </c>
       <c r="D390" t="n">
-        <v>24290</v>
+        <v>28244</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>95.7</v>
+        <v>137.13</v>
       </c>
       <c r="B391" t="n">
-        <v>38929</v>
+        <v>19468</v>
       </c>
       <c r="C391" t="n">
-        <v>92.62</v>
+        <v>138.32</v>
       </c>
       <c r="D391" t="n">
-        <v>10115</v>
+        <v>29711</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>107.74</v>
+        <v>137.22</v>
       </c>
       <c r="B392" t="n">
-        <v>40180</v>
+        <v>18399</v>
       </c>
       <c r="C392" t="n">
-        <v>106.95</v>
+        <v>145.45</v>
       </c>
       <c r="D392" t="n">
-        <v>10235</v>
+        <v>13251</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>110.36</v>
+        <v>137.23</v>
       </c>
       <c r="B393" t="n">
-        <v>29625</v>
+        <v>18795</v>
       </c>
       <c r="C393" t="n">
-        <v>106.3</v>
+        <v>125.94</v>
       </c>
       <c r="D393" t="n">
-        <v>17675</v>
+        <v>28896</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>93.83</v>
+        <v>138.05</v>
       </c>
       <c r="B394" t="n">
-        <v>27635</v>
+        <v>19553</v>
       </c>
       <c r="C394" t="n">
-        <v>94.68000000000001</v>
+        <v>132.94</v>
       </c>
       <c r="D394" t="n">
-        <v>21734</v>
+        <v>24600</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>55.62</v>
+        <v>138.94</v>
       </c>
       <c r="B395" t="n">
-        <v>22164</v>
+        <v>19080</v>
       </c>
       <c r="C395" t="n">
-        <v>58.13</v>
+        <v>145.93</v>
       </c>
       <c r="D395" t="n">
-        <v>17946</v>
+        <v>20141</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>108.25</v>
+        <v>139.3</v>
       </c>
       <c r="B396" t="n">
-        <v>41058</v>
+        <v>19914</v>
       </c>
       <c r="C396" t="n">
-        <v>107.47</v>
+        <v>146.65</v>
       </c>
       <c r="D396" t="n">
-        <v>23175</v>
+        <v>21203</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>68.52</v>
+        <v>139.51</v>
       </c>
       <c r="B397" t="n">
-        <v>22953</v>
+        <v>19353</v>
       </c>
       <c r="C397" t="n">
-        <v>67.08</v>
+        <v>161.02</v>
       </c>
       <c r="D397" t="n">
-        <v>14862</v>
+        <v>16968</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>114.01</v>
+        <v>139.79</v>
       </c>
       <c r="B398" t="n">
-        <v>23212</v>
+        <v>19284</v>
       </c>
       <c r="C398" t="n">
-        <v>115.91</v>
+        <v>129.84</v>
       </c>
       <c r="D398" t="n">
-        <v>22672</v>
+        <v>24507</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>108.74</v>
+        <v>140.25</v>
       </c>
       <c r="B399" t="n">
-        <v>35341</v>
+        <v>19523</v>
       </c>
       <c r="C399" t="n">
-        <v>108.91</v>
+        <v>130.14</v>
       </c>
       <c r="D399" t="n">
-        <v>18208</v>
+        <v>18274</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>98.08</v>
+        <v>140.31</v>
       </c>
       <c r="B400" t="n">
-        <v>42319</v>
+        <v>19483</v>
       </c>
       <c r="C400" t="n">
-        <v>98.39</v>
+        <v>170.7</v>
       </c>
       <c r="D400" t="n">
-        <v>29149</v>
+        <v>20904</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>103.78</v>
+        <v>140.68</v>
       </c>
       <c r="B401" t="n">
-        <v>47897</v>
+        <v>20577</v>
       </c>
       <c r="C401" t="n">
-        <v>101.43</v>
+        <v>158.47</v>
       </c>
       <c r="D401" t="n">
-        <v>20620</v>
+        <v>20254</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>104.1</v>
+        <v>140.68</v>
       </c>
       <c r="B402" t="n">
-        <v>44846</v>
+        <v>18576</v>
       </c>
       <c r="C402" t="n">
-        <v>107.04</v>
+        <v>119.77</v>
       </c>
       <c r="D402" t="n">
-        <v>17797</v>
+        <v>26699</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>112.09</v>
+        <v>141.21</v>
       </c>
       <c r="B403" t="n">
-        <v>27281</v>
+        <v>16908</v>
       </c>
       <c r="C403" t="n">
-        <v>109.13</v>
+        <v>131.1</v>
       </c>
       <c r="D403" t="n">
-        <v>18432</v>
+        <v>12223</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>103.35</v>
+        <v>141.27</v>
       </c>
       <c r="B404" t="n">
-        <v>47819</v>
+        <v>19623</v>
       </c>
       <c r="C404" t="n">
-        <v>103.89</v>
+        <v>130.82</v>
       </c>
       <c r="D404" t="n">
-        <v>15325</v>
+        <v>24765</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>103.23</v>
+        <v>141.69</v>
       </c>
       <c r="B405" t="n">
-        <v>48377</v>
+        <v>21050</v>
       </c>
       <c r="C405" t="n">
-        <v>105</v>
+        <v>152.24</v>
       </c>
       <c r="D405" t="n">
-        <v>16105</v>
+        <v>14630</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>105.62</v>
+        <v>141.82</v>
       </c>
       <c r="B406" t="n">
-        <v>42148</v>
+        <v>21592</v>
       </c>
       <c r="C406" t="n">
-        <v>103.29</v>
+        <v>137.2</v>
       </c>
       <c r="D406" t="n">
-        <v>14148</v>
+        <v>20258</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>138.35</v>
+        <v>142.37</v>
       </c>
       <c r="B407" t="n">
-        <v>22027</v>
+        <v>19128</v>
       </c>
       <c r="C407" t="n">
-        <v>142.52</v>
+        <v>126.55</v>
       </c>
       <c r="D407" t="n">
-        <v>19368</v>
+        <v>25408</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>103.26</v>
+        <v>142.78</v>
       </c>
       <c r="B408" t="n">
-        <v>49059</v>
+        <v>19023</v>
       </c>
       <c r="C408" t="n">
-        <v>103.42</v>
+        <v>151.99</v>
       </c>
       <c r="D408" t="n">
-        <v>11474</v>
+        <v>14334</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>92.67</v>
+        <v>143.02</v>
       </c>
       <c r="B409" t="n">
-        <v>28846</v>
+        <v>20162</v>
       </c>
       <c r="C409" t="n">
-        <v>90.04000000000001</v>
+        <v>160.89</v>
       </c>
       <c r="D409" t="n">
-        <v>18863</v>
+        <v>28629</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>93.26000000000001</v>
+        <v>144.01</v>
       </c>
       <c r="B410" t="n">
-        <v>30669</v>
+        <v>20469</v>
       </c>
       <c r="C410" t="n">
-        <v>95.16</v>
+        <v>151.22</v>
       </c>
       <c r="D410" t="n">
-        <v>20144</v>
+        <v>14553</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>101.82</v>
+        <v>144.49</v>
       </c>
       <c r="B411" t="n">
-        <v>46477</v>
+        <v>18500</v>
       </c>
       <c r="C411" t="n">
-        <v>97.84</v>
+        <v>147.38</v>
       </c>
       <c r="D411" t="n">
-        <v>16456</v>
+        <v>16079</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>1.68</v>
+        <v>144.85</v>
       </c>
       <c r="B412" t="n">
-        <v>23007</v>
+        <v>20744</v>
       </c>
       <c r="C412" t="n">
-        <v>1.61</v>
+        <v>154.95</v>
       </c>
       <c r="D412" t="n">
-        <v>26151</v>
+        <v>29102</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>102.41</v>
+        <v>144.92</v>
       </c>
       <c r="B413" t="n">
-        <v>46583</v>
+        <v>19883</v>
       </c>
       <c r="C413" t="n">
-        <v>101.28</v>
+        <v>176.21</v>
       </c>
       <c r="D413" t="n">
-        <v>12985</v>
+        <v>10283</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>109.99</v>
+        <v>145.12</v>
       </c>
       <c r="B414" t="n">
-        <v>31337</v>
+        <v>18702</v>
       </c>
       <c r="C414" t="n">
-        <v>113.89</v>
+        <v>117.37</v>
       </c>
       <c r="D414" t="n">
-        <v>29037</v>
+        <v>10504</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>89.76000000000001</v>
+        <v>145.47</v>
       </c>
       <c r="B415" t="n">
-        <v>23628</v>
+        <v>20778</v>
       </c>
       <c r="C415" t="n">
-        <v>91.76000000000001</v>
+        <v>164.63</v>
       </c>
       <c r="D415" t="n">
-        <v>15468</v>
+        <v>21384</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>109.33</v>
+        <v>146.69</v>
       </c>
       <c r="B416" t="n">
-        <v>33301</v>
+        <v>20718</v>
       </c>
       <c r="C416" t="n">
-        <v>110.59</v>
+        <v>152.34</v>
       </c>
       <c r="D416" t="n">
-        <v>14875</v>
+        <v>12223</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>91.92</v>
+        <v>146.78</v>
       </c>
       <c r="B417" t="n">
-        <v>27297</v>
+        <v>22921</v>
       </c>
       <c r="C417" t="n">
-        <v>93.42</v>
+        <v>123.98</v>
       </c>
       <c r="D417" t="n">
-        <v>16460</v>
+        <v>12768</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>92.11</v>
+        <v>146.96</v>
       </c>
       <c r="B418" t="n">
-        <v>27394</v>
+        <v>22548</v>
       </c>
       <c r="C418" t="n">
-        <v>93.7</v>
+        <v>121.93</v>
       </c>
       <c r="D418" t="n">
-        <v>21549</v>
+        <v>10085</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>24.53</v>
+        <v>147.59</v>
       </c>
       <c r="B419" t="n">
-        <v>23919</v>
+        <v>22420</v>
       </c>
       <c r="C419" t="n">
-        <v>25.59</v>
+        <v>148.19</v>
       </c>
       <c r="D419" t="n">
-        <v>29717</v>
+        <v>16605</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>40.79</v>
+        <v>147.9</v>
       </c>
       <c r="B420" t="n">
-        <v>25731</v>
+        <v>20147</v>
       </c>
       <c r="C420" t="n">
-        <v>41.05</v>
+        <v>119.63</v>
       </c>
       <c r="D420" t="n">
-        <v>19555</v>
+        <v>14372</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>84.58</v>
+        <v>148.13</v>
       </c>
       <c r="B421" t="n">
-        <v>24215</v>
+        <v>23024</v>
       </c>
       <c r="C421" t="n">
-        <v>82.48999999999999</v>
+        <v>119.63</v>
       </c>
       <c r="D421" t="n">
-        <v>29319</v>
+        <v>23570</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>92.61</v>
+        <v>148.7</v>
       </c>
       <c r="B422" t="n">
-        <v>29609</v>
+        <v>24223</v>
       </c>
       <c r="C422" t="n">
-        <v>93.79000000000001</v>
+        <v>174.35</v>
       </c>
       <c r="D422" t="n">
-        <v>26630</v>
+        <v>27957</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>91.40000000000001</v>
+        <v>148.74</v>
       </c>
       <c r="B423" t="n">
-        <v>25200</v>
+        <v>18605</v>
       </c>
       <c r="C423" t="n">
-        <v>89.42</v>
+        <v>124.45</v>
       </c>
       <c r="D423" t="n">
-        <v>26258</v>
+        <v>22278</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>109.53</v>
+        <v>150.08</v>
       </c>
       <c r="B424" t="n">
-        <v>34848</v>
+        <v>23353</v>
       </c>
       <c r="C424" t="n">
-        <v>112.78</v>
+        <v>130.97</v>
       </c>
       <c r="D424" t="n">
-        <v>10671</v>
+        <v>27721</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>103.46</v>
+        <v>150.53</v>
       </c>
       <c r="B425" t="n">
-        <v>47834</v>
+        <v>23300</v>
       </c>
       <c r="C425" t="n">
-        <v>100.18</v>
+        <v>118.09</v>
       </c>
       <c r="D425" t="n">
-        <v>28966</v>
+        <v>13949</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>25.19</v>
+        <v>150.71</v>
       </c>
       <c r="B426" t="n">
-        <v>24701</v>
+        <v>26936</v>
       </c>
       <c r="C426" t="n">
-        <v>24.75</v>
+        <v>137.12</v>
       </c>
       <c r="D426" t="n">
-        <v>26583</v>
+        <v>24732</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>115.95</v>
+        <v>151.64</v>
       </c>
       <c r="B427" t="n">
-        <v>24121</v>
+        <v>24125</v>
       </c>
       <c r="C427" t="n">
-        <v>115.5</v>
+        <v>162.86</v>
       </c>
       <c r="D427" t="n">
-        <v>24138</v>
+        <v>28650</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>108.84</v>
+        <v>152.96</v>
       </c>
       <c r="B428" t="n">
-        <v>33659</v>
+        <v>27124</v>
       </c>
       <c r="C428" t="n">
-        <v>106.93</v>
+        <v>144.03</v>
       </c>
       <c r="D428" t="n">
-        <v>27501</v>
+        <v>13603</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>111.02</v>
+        <v>153.36</v>
       </c>
       <c r="B429" t="n">
-        <v>30395</v>
+        <v>25240</v>
       </c>
       <c r="C429" t="n">
-        <v>110.18</v>
+        <v>119.63</v>
       </c>
       <c r="D429" t="n">
-        <v>29660</v>
+        <v>25087</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>107.46</v>
+        <v>153.43</v>
       </c>
       <c r="B430" t="n">
-        <v>40406</v>
+        <v>25518</v>
       </c>
       <c r="C430" t="n">
-        <v>108.82</v>
+        <v>172.11</v>
       </c>
       <c r="D430" t="n">
-        <v>11695</v>
+        <v>10737</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>93.68000000000001</v>
+        <v>154.09</v>
       </c>
       <c r="B431" t="n">
-        <v>31306</v>
+        <v>27418</v>
       </c>
       <c r="C431" t="n">
-        <v>92.01000000000001</v>
+        <v>149.31</v>
       </c>
       <c r="D431" t="n">
-        <v>11010</v>
+        <v>28495</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>95.67</v>
+        <v>154.13</v>
       </c>
       <c r="B432" t="n">
-        <v>34645</v>
+        <v>27125</v>
       </c>
       <c r="C432" t="n">
-        <v>97.29000000000001</v>
+        <v>140.34</v>
       </c>
       <c r="D432" t="n">
-        <v>12387</v>
+        <v>13990</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>80.67</v>
+        <v>154.73</v>
       </c>
       <c r="B433" t="n">
-        <v>25167</v>
+        <v>29264</v>
       </c>
       <c r="C433" t="n">
-        <v>79.23</v>
+        <v>127.42</v>
       </c>
       <c r="D433" t="n">
-        <v>29413</v>
+        <v>13753</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>111.87</v>
+        <v>155.69</v>
       </c>
       <c r="B434" t="n">
-        <v>29111</v>
+        <v>29322</v>
       </c>
       <c r="C434" t="n">
-        <v>108.77</v>
+        <v>161.53</v>
       </c>
       <c r="D434" t="n">
-        <v>22849</v>
+        <v>21161</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>127.17</v>
+        <v>155.74</v>
       </c>
       <c r="B435" t="n">
-        <v>23082</v>
+        <v>27202</v>
       </c>
       <c r="C435" t="n">
-        <v>125.48</v>
+        <v>176.13</v>
       </c>
       <c r="D435" t="n">
-        <v>25885</v>
+        <v>20204</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>104.7</v>
+        <v>156.13</v>
       </c>
       <c r="B436" t="n">
-        <v>46819</v>
+        <v>27977</v>
       </c>
       <c r="C436" t="n">
-        <v>103.25</v>
+        <v>133.88</v>
       </c>
       <c r="D436" t="n">
-        <v>13229</v>
+        <v>21675</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>113.93</v>
+        <v>156.83</v>
       </c>
       <c r="B437" t="n">
-        <v>24809</v>
+        <v>32157</v>
       </c>
       <c r="C437" t="n">
-        <v>109.81</v>
+        <v>140.42</v>
       </c>
       <c r="D437" t="n">
-        <v>21428</v>
+        <v>10593</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>114.99</v>
+        <v>157.01</v>
       </c>
       <c r="B438" t="n">
-        <v>22550</v>
+        <v>28206</v>
       </c>
       <c r="C438" t="n">
-        <v>119.9</v>
+        <v>164.71</v>
       </c>
       <c r="D438" t="n">
-        <v>10009</v>
+        <v>20331</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>3.57</v>
+        <v>157.28</v>
       </c>
       <c r="B439" t="n">
-        <v>23344</v>
+        <v>30911</v>
       </c>
       <c r="C439" t="n">
-        <v>3.48</v>
+        <v>135.13</v>
       </c>
       <c r="D439" t="n">
-        <v>19021</v>
+        <v>27740</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>95.45999999999999</v>
+        <v>157.42</v>
       </c>
       <c r="B440" t="n">
-        <v>35908</v>
+        <v>32248</v>
       </c>
       <c r="C440" t="n">
-        <v>98.97</v>
+        <v>129.48</v>
       </c>
       <c r="D440" t="n">
-        <v>29591</v>
+        <v>20684</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>109.65</v>
+        <v>157.86</v>
       </c>
       <c r="B441" t="n">
-        <v>36363</v>
+        <v>28912</v>
       </c>
       <c r="C441" t="n">
-        <v>107.55</v>
+        <v>167.5</v>
       </c>
       <c r="D441" t="n">
-        <v>25230</v>
+        <v>13307</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>99.59999999999999</v>
+        <v>158.06</v>
       </c>
       <c r="B442" t="n">
-        <v>43145</v>
+        <v>31210</v>
       </c>
       <c r="C442" t="n">
-        <v>103.29</v>
+        <v>159.79</v>
       </c>
       <c r="D442" t="n">
-        <v>10619</v>
+        <v>22828</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>125.2</v>
+        <v>158.37</v>
       </c>
       <c r="B443" t="n">
-        <v>24344</v>
+        <v>32635</v>
       </c>
       <c r="C443" t="n">
-        <v>121.03</v>
+        <v>166.2</v>
       </c>
       <c r="D443" t="n">
-        <v>18776</v>
+        <v>26478</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>52.36</v>
+        <v>159.07</v>
       </c>
       <c r="B444" t="n">
-        <v>25164</v>
+        <v>29814</v>
       </c>
       <c r="C444" t="n">
-        <v>51.23</v>
+        <v>144.79</v>
       </c>
       <c r="D444" t="n">
-        <v>11019</v>
+        <v>18933</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>100.87</v>
+        <v>159.29</v>
       </c>
       <c r="B445" t="n">
-        <v>46354</v>
+        <v>32327</v>
       </c>
       <c r="C445" t="n">
-        <v>102.59</v>
+        <v>167.11</v>
       </c>
       <c r="D445" t="n">
-        <v>13733</v>
+        <v>20249</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>125.6</v>
+        <v>159.89</v>
       </c>
       <c r="B446" t="n">
-        <v>25400</v>
+        <v>31538</v>
       </c>
       <c r="C446" t="n">
-        <v>121.6</v>
+        <v>162.98</v>
       </c>
       <c r="D446" t="n">
-        <v>26805</v>
+        <v>27076</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>103.37</v>
+        <v>160.72</v>
       </c>
       <c r="B447" t="n">
-        <v>47403</v>
+        <v>31931</v>
       </c>
       <c r="C447" t="n">
-        <v>102.89</v>
+        <v>180</v>
       </c>
       <c r="D447" t="n">
-        <v>15650</v>
+        <v>17769</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>94.29000000000001</v>
+        <v>161.8</v>
       </c>
       <c r="B448" t="n">
-        <v>32393</v>
+        <v>29767</v>
       </c>
       <c r="C448" t="n">
-        <v>94.20999999999999</v>
+        <v>169.9</v>
       </c>
       <c r="D448" t="n">
-        <v>17034</v>
+        <v>13489</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>101.23</v>
+        <v>161.87</v>
       </c>
       <c r="B449" t="n">
-        <v>47253</v>
+        <v>30350</v>
       </c>
       <c r="C449" t="n">
-        <v>103.71</v>
+        <v>138.29</v>
       </c>
       <c r="D449" t="n">
-        <v>15329</v>
+        <v>25285</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>103.17</v>
+        <v>162.76</v>
       </c>
       <c r="B450" t="n">
-        <v>47344</v>
+        <v>32005</v>
       </c>
       <c r="C450" t="n">
-        <v>104.89</v>
+        <v>177.1</v>
       </c>
       <c r="D450" t="n">
-        <v>26260</v>
+        <v>12845</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>98.23</v>
+        <v>163.18</v>
       </c>
       <c r="B451" t="n">
-        <v>41757</v>
+        <v>30919</v>
       </c>
       <c r="C451" t="n">
-        <v>95.23</v>
+        <v>180</v>
       </c>
       <c r="D451" t="n">
-        <v>15001</v>
+        <v>10718</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>139.75</v>
+        <v>163.46</v>
       </c>
       <c r="B452" t="n">
-        <v>23538</v>
+        <v>31278</v>
       </c>
       <c r="C452" t="n">
-        <v>135.95</v>
+        <v>174.69</v>
       </c>
       <c r="D452" t="n">
-        <v>16020</v>
+        <v>24635</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>91.5</v>
+        <v>163.55</v>
       </c>
       <c r="B453" t="n">
-        <v>24781</v>
+        <v>27720</v>
       </c>
       <c r="C453" t="n">
-        <v>93.56</v>
+        <v>180</v>
       </c>
       <c r="D453" t="n">
-        <v>23782</v>
+        <v>23890</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>95.19</v>
+        <v>163.84</v>
       </c>
       <c r="B454" t="n">
-        <v>32606</v>
+        <v>29529</v>
       </c>
       <c r="C454" t="n">
-        <v>92.11</v>
+        <v>158.2</v>
       </c>
       <c r="D454" t="n">
-        <v>17029</v>
+        <v>10929</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>100.18</v>
+        <v>164.15</v>
       </c>
       <c r="B455" t="n">
-        <v>45185</v>
+        <v>26935</v>
       </c>
       <c r="C455" t="n">
-        <v>101.73</v>
+        <v>132.04</v>
       </c>
       <c r="D455" t="n">
-        <v>20647</v>
+        <v>13930</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>105.29</v>
+        <v>164.33</v>
       </c>
       <c r="B456" t="n">
-        <v>45562</v>
+        <v>30019</v>
       </c>
       <c r="C456" t="n">
-        <v>104.78</v>
+        <v>143.47</v>
       </c>
       <c r="D456" t="n">
-        <v>28220</v>
+        <v>12095</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>97.98999999999999</v>
+        <v>165.54</v>
       </c>
       <c r="B457" t="n">
-        <v>40765</v>
+        <v>28621</v>
       </c>
       <c r="C457" t="n">
-        <v>100.21</v>
+        <v>180</v>
       </c>
       <c r="D457" t="n">
-        <v>16496</v>
+        <v>26709</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>111.55</v>
+        <v>165.57</v>
       </c>
       <c r="B458" t="n">
-        <v>30840</v>
+        <v>27941</v>
       </c>
       <c r="C458" t="n">
-        <v>114.64</v>
+        <v>138.44</v>
       </c>
       <c r="D458" t="n">
-        <v>21881</v>
+        <v>13138</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>92.98999999999999</v>
+        <v>165.6</v>
       </c>
       <c r="B459" t="n">
-        <v>27644</v>
+        <v>27866</v>
       </c>
       <c r="C459" t="n">
-        <v>93.52</v>
+        <v>180</v>
       </c>
       <c r="D459" t="n">
-        <v>27845</v>
+        <v>17578</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>106.95</v>
+        <v>165.66</v>
       </c>
       <c r="B460" t="n">
-        <v>40088</v>
+        <v>28536</v>
       </c>
       <c r="C460" t="n">
-        <v>108.03</v>
+        <v>143.07</v>
       </c>
       <c r="D460" t="n">
-        <v>21386</v>
+        <v>21725</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>95.95</v>
+        <v>165.79</v>
       </c>
       <c r="B461" t="n">
-        <v>36609</v>
+        <v>28286</v>
       </c>
       <c r="C461" t="n">
-        <v>93.66</v>
+        <v>180</v>
       </c>
       <c r="D461" t="n">
-        <v>23460</v>
+        <v>28548</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>2.5</v>
+        <v>165.8</v>
       </c>
       <c r="B462" t="n">
-        <v>22051</v>
+        <v>28727</v>
       </c>
       <c r="C462" t="n">
-        <v>2.59</v>
+        <v>147.77</v>
       </c>
       <c r="D462" t="n">
-        <v>21468</v>
+        <v>23753</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>102.78</v>
+        <v>166.24</v>
       </c>
       <c r="B463" t="n">
-        <v>50065</v>
+        <v>26244</v>
       </c>
       <c r="C463" t="n">
-        <v>104.6</v>
+        <v>178.65</v>
       </c>
       <c r="D463" t="n">
-        <v>27025</v>
+        <v>20789</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>62.84</v>
+        <v>166.48</v>
       </c>
       <c r="B464" t="n">
-        <v>25627</v>
+        <v>27521</v>
       </c>
       <c r="C464" t="n">
-        <v>61.86</v>
+        <v>154.33</v>
       </c>
       <c r="D464" t="n">
-        <v>22762</v>
+        <v>19261</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>94.05</v>
+        <v>166.57</v>
       </c>
       <c r="B465" t="n">
-        <v>29641</v>
+        <v>25842</v>
       </c>
       <c r="C465" t="n">
-        <v>92.52</v>
+        <v>180</v>
       </c>
       <c r="D465" t="n">
-        <v>16114</v>
+        <v>21832</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>107.78</v>
+        <v>167.1</v>
       </c>
       <c r="B466" t="n">
-        <v>38644</v>
+        <v>25122</v>
       </c>
       <c r="C466" t="n">
-        <v>106.14</v>
+        <v>156.95</v>
       </c>
       <c r="D466" t="n">
-        <v>14870</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>100.31</v>
+        <v>167.28</v>
       </c>
       <c r="B467" t="n">
-        <v>43362</v>
+        <v>27315</v>
       </c>
       <c r="C467" t="n">
-        <v>97.72</v>
+        <v>146.45</v>
       </c>
       <c r="D467" t="n">
-        <v>17157</v>
+        <v>28665</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>105.99</v>
+        <v>167.62</v>
       </c>
       <c r="B468" t="n">
-        <v>44009</v>
+        <v>25811</v>
       </c>
       <c r="C468" t="n">
-        <v>108.11</v>
+        <v>152.75</v>
       </c>
       <c r="D468" t="n">
-        <v>19796</v>
+        <v>18939</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>105.12</v>
+        <v>168.64</v>
       </c>
       <c r="B469" t="n">
-        <v>44669</v>
+        <v>24534</v>
       </c>
       <c r="C469" t="n">
-        <v>101.24</v>
+        <v>167.21</v>
       </c>
       <c r="D469" t="n">
-        <v>11324</v>
+        <v>14208</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>107.39</v>
+        <v>168.87</v>
       </c>
       <c r="B470" t="n">
-        <v>39887</v>
+        <v>23011</v>
       </c>
       <c r="C470" t="n">
-        <v>103.34</v>
+        <v>147.96</v>
       </c>
       <c r="D470" t="n">
-        <v>20277</v>
+        <v>16496</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>99.04000000000001</v>
+        <v>168.96</v>
       </c>
       <c r="B471" t="n">
-        <v>43299</v>
+        <v>24438</v>
       </c>
       <c r="C471" t="n">
-        <v>99.52</v>
+        <v>177.81</v>
       </c>
       <c r="D471" t="n">
-        <v>24999</v>
+        <v>24545</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>100.46</v>
+        <v>170.06</v>
       </c>
       <c r="B472" t="n">
-        <v>46262</v>
+        <v>23629</v>
       </c>
       <c r="C472" t="n">
-        <v>103.64</v>
+        <v>168.75</v>
       </c>
       <c r="D472" t="n">
-        <v>22354</v>
+        <v>15960</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>102.46</v>
+        <v>170.37</v>
       </c>
       <c r="B473" t="n">
-        <v>46998</v>
+        <v>22932</v>
       </c>
       <c r="C473" t="n">
-        <v>99.02</v>
+        <v>167.11</v>
       </c>
       <c r="D473" t="n">
-        <v>27571</v>
+        <v>14023</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>109.06</v>
+        <v>170.56</v>
       </c>
       <c r="B474" t="n">
-        <v>37977</v>
+        <v>23473</v>
       </c>
       <c r="C474" t="n">
-        <v>111.58</v>
+        <v>156.11</v>
       </c>
       <c r="D474" t="n">
-        <v>14450</v>
+        <v>18824</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>16.67</v>
+        <v>170.71</v>
       </c>
       <c r="B475" t="n">
-        <v>26527</v>
+        <v>23245</v>
       </c>
       <c r="C475" t="n">
-        <v>16.7</v>
+        <v>180</v>
       </c>
       <c r="D475" t="n">
-        <v>22454</v>
+        <v>14103</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>107.51</v>
+        <v>170.82</v>
       </c>
       <c r="B476" t="n">
-        <v>40255</v>
+        <v>22563</v>
       </c>
       <c r="C476" t="n">
-        <v>108.92</v>
+        <v>164.66</v>
       </c>
       <c r="D476" t="n">
-        <v>22154</v>
+        <v>21185</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>90.90000000000001</v>
+        <v>171.72</v>
       </c>
       <c r="B477" t="n">
-        <v>23773</v>
+        <v>19550</v>
       </c>
       <c r="C477" t="n">
-        <v>87.70999999999999</v>
+        <v>178.73</v>
       </c>
       <c r="D477" t="n">
-        <v>10073</v>
+        <v>22107</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>96.76000000000001</v>
+        <v>172.33</v>
       </c>
       <c r="B478" t="n">
-        <v>36631</v>
+        <v>21558</v>
       </c>
       <c r="C478" t="n">
-        <v>97.47</v>
+        <v>173.23</v>
       </c>
       <c r="D478" t="n">
-        <v>20450</v>
+        <v>17585</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>145.17</v>
+        <v>172.34</v>
       </c>
       <c r="B479" t="n">
-        <v>22544</v>
+        <v>22988</v>
       </c>
       <c r="C479" t="n">
-        <v>145.96</v>
+        <v>180</v>
       </c>
       <c r="D479" t="n">
-        <v>18674</v>
+        <v>28644</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>93.58</v>
+        <v>172.6</v>
       </c>
       <c r="B480" t="n">
-        <v>31105</v>
+        <v>19879</v>
       </c>
       <c r="C480" t="n">
-        <v>95.15000000000001</v>
+        <v>159.58</v>
       </c>
       <c r="D480" t="n">
-        <v>17169</v>
+        <v>21084</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>94.81999999999999</v>
+        <v>172.92</v>
       </c>
       <c r="B481" t="n">
-        <v>32540</v>
+        <v>18904</v>
       </c>
       <c r="C481" t="n">
-        <v>96.26000000000001</v>
+        <v>180</v>
       </c>
       <c r="D481" t="n">
-        <v>17544</v>
+        <v>10046</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>104.12</v>
+        <v>173.08</v>
       </c>
       <c r="B482" t="n">
-        <v>44878</v>
+        <v>19922</v>
       </c>
       <c r="C482" t="n">
-        <v>104.03</v>
+        <v>145.68</v>
       </c>
       <c r="D482" t="n">
-        <v>25145</v>
+        <v>26841</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>44.76</v>
+        <v>173.31</v>
       </c>
       <c r="B483" t="n">
-        <v>25131</v>
+        <v>21544</v>
       </c>
       <c r="C483" t="n">
-        <v>43.08</v>
+        <v>180</v>
       </c>
       <c r="D483" t="n">
-        <v>14481</v>
+        <v>14100</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>94.75</v>
+        <v>173.53</v>
       </c>
       <c r="B484" t="n">
-        <v>32694</v>
+        <v>21313</v>
       </c>
       <c r="C484" t="n">
-        <v>93.66</v>
+        <v>180</v>
       </c>
       <c r="D484" t="n">
-        <v>10946</v>
+        <v>20974</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>99.37</v>
+        <v>173.67</v>
       </c>
       <c r="B485" t="n">
-        <v>43352</v>
+        <v>21090</v>
       </c>
       <c r="C485" t="n">
-        <v>101.23</v>
+        <v>180</v>
       </c>
       <c r="D485" t="n">
-        <v>11952</v>
+        <v>17383</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>98.86</v>
+        <v>174.07</v>
       </c>
       <c r="B486" t="n">
-        <v>42420</v>
+        <v>17026</v>
       </c>
       <c r="C486" t="n">
-        <v>98.41</v>
+        <v>179.13</v>
       </c>
       <c r="D486" t="n">
-        <v>25391</v>
+        <v>24305</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>92.59</v>
+        <v>174.25</v>
       </c>
       <c r="B487" t="n">
-        <v>26239</v>
+        <v>20295</v>
       </c>
       <c r="C487" t="n">
-        <v>94.13</v>
+        <v>178.4</v>
       </c>
       <c r="D487" t="n">
-        <v>16619</v>
+        <v>18386</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>99.23</v>
+        <v>174.39</v>
       </c>
       <c r="B488" t="n">
-        <v>41230</v>
+        <v>22810</v>
       </c>
       <c r="C488" t="n">
-        <v>102.95</v>
+        <v>157.73</v>
       </c>
       <c r="D488" t="n">
-        <v>12122</v>
+        <v>23385</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>62.63</v>
+        <v>174.46</v>
       </c>
       <c r="B489" t="n">
-        <v>23245</v>
+        <v>18911</v>
       </c>
       <c r="C489" t="n">
-        <v>62.01</v>
+        <v>157.55</v>
       </c>
       <c r="D489" t="n">
-        <v>21791</v>
+        <v>11365</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>98.37</v>
+        <v>174.48</v>
       </c>
       <c r="B490" t="n">
-        <v>41267</v>
+        <v>20470</v>
       </c>
       <c r="C490" t="n">
-        <v>100.16</v>
+        <v>148.76</v>
       </c>
       <c r="D490" t="n">
-        <v>18171</v>
+        <v>10081</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>93.22</v>
+        <v>175.44</v>
       </c>
       <c r="B491" t="n">
-        <v>30236</v>
+        <v>18588</v>
       </c>
       <c r="C491" t="n">
-        <v>90.54000000000001</v>
+        <v>162.12</v>
       </c>
       <c r="D491" t="n">
-        <v>11433</v>
+        <v>29763</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>71.09999999999999</v>
+        <v>175.55</v>
       </c>
       <c r="B492" t="n">
-        <v>23583</v>
+        <v>17149</v>
       </c>
       <c r="C492" t="n">
-        <v>70.34999999999999</v>
+        <v>180</v>
       </c>
       <c r="D492" t="n">
-        <v>17899</v>
+        <v>26706</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>87.94</v>
+        <v>176.79</v>
       </c>
       <c r="B493" t="n">
-        <v>26889</v>
+        <v>18186</v>
       </c>
       <c r="C493" t="n">
-        <v>87.84999999999999</v>
+        <v>158.82</v>
       </c>
       <c r="D493" t="n">
-        <v>26641</v>
+        <v>10787</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>100.72</v>
+        <v>177.16</v>
       </c>
       <c r="B494" t="n">
-        <v>45725</v>
+        <v>18283</v>
       </c>
       <c r="C494" t="n">
-        <v>99.28</v>
+        <v>172.59</v>
       </c>
       <c r="D494" t="n">
-        <v>20572</v>
+        <v>12933</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>54.78</v>
+        <v>177.48</v>
       </c>
       <c r="B495" t="n">
-        <v>25837</v>
+        <v>18558</v>
       </c>
       <c r="C495" t="n">
-        <v>54.6</v>
+        <v>137.7</v>
       </c>
       <c r="D495" t="n">
-        <v>29709</v>
+        <v>20569</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>96.52</v>
+        <v>178.13</v>
       </c>
       <c r="B496" t="n">
-        <v>38788</v>
+        <v>17749</v>
       </c>
       <c r="C496" t="n">
-        <v>94.05</v>
+        <v>145.13</v>
       </c>
       <c r="D496" t="n">
-        <v>19790</v>
+        <v>10641</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>81.16</v>
+        <v>178.4</v>
       </c>
       <c r="B497" t="n">
-        <v>26456</v>
+        <v>19438</v>
       </c>
       <c r="C497" t="n">
-        <v>77.09</v>
+        <v>180</v>
       </c>
       <c r="D497" t="n">
-        <v>28149</v>
+        <v>10220</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>99.44</v>
+        <v>178.64</v>
       </c>
       <c r="B498" t="n">
-        <v>43505</v>
+        <v>18726</v>
       </c>
       <c r="C498" t="n">
-        <v>95.89</v>
+        <v>158.77</v>
       </c>
       <c r="D498" t="n">
-        <v>10177</v>
+        <v>15555</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>90.66</v>
+        <v>179.12</v>
       </c>
       <c r="B499" t="n">
-        <v>20293</v>
+        <v>18002</v>
       </c>
       <c r="C499" t="n">
-        <v>90.69</v>
+        <v>180</v>
       </c>
       <c r="D499" t="n">
-        <v>23869</v>
+        <v>25423</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>113.31</v>
+        <v>179.13</v>
       </c>
       <c r="B500" t="n">
-        <v>25109</v>
+        <v>19901</v>
       </c>
       <c r="C500" t="n">
-        <v>109.52</v>
+        <v>156.86</v>
       </c>
       <c r="D500" t="n">
-        <v>12196</v>
+        <v>20767</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>105.38</v>
+        <v>179.51</v>
       </c>
       <c r="B501" t="n">
-        <v>46622</v>
+        <v>16289</v>
       </c>
       <c r="C501" t="n">
-        <v>101.65</v>
+        <v>180</v>
       </c>
       <c r="D501" t="n">
-        <v>23417</v>
+        <v>19327</v>
       </c>
     </row>
   </sheetData>
